--- a/flash.xlsx
+++ b/flash.xlsx
@@ -912,682 +912,686 @@
     <t>9x9</t>
   </si>
   <si>
-    <t>images/GH.jpg</t>
-  </si>
-  <si>
-    <t>images/GA.jpg</t>
-  </si>
-  <si>
-    <t>images/GY.jpg</t>
-  </si>
-  <si>
-    <t>images/GM.jpg</t>
-  </si>
-  <si>
-    <t>images/GG.jpg</t>
-  </si>
-  <si>
-    <t>images/GP.jpg</t>
-  </si>
-  <si>
-    <t>images/GT.jpg</t>
-  </si>
-  <si>
-    <t>images/GU.jpg</t>
-  </si>
-  <si>
-    <t>images/GD.jpg</t>
-  </si>
-  <si>
-    <t>images/GR.jpg</t>
-  </si>
-  <si>
-    <t>images/GL.jpg</t>
-  </si>
-  <si>
-    <t>images/GN.jpg</t>
-  </si>
-  <si>
-    <t>images/GW.jpg</t>
-  </si>
-  <si>
-    <t>images/NA.jpg</t>
-  </si>
-  <si>
-    <t>images/NR.jpg</t>
-  </si>
-  <si>
-    <t>images/NG.jpg</t>
-  </si>
-  <si>
-    <t>images/SS.jpg</t>
-  </si>
-  <si>
-    <t>images/ZA.jpg</t>
-  </si>
-  <si>
-    <t>images/NL.jpg</t>
-  </si>
-  <si>
-    <t>images/AN.jpg</t>
-  </si>
-  <si>
-    <t>images/NP.jpg</t>
-  </si>
-  <si>
-    <t>images/NO.jpg</t>
-  </si>
-  <si>
-    <t>images/NC.jpg</t>
-  </si>
-  <si>
-    <t>images/NZ.jpg</t>
-  </si>
-  <si>
-    <t>images/NU.jpg</t>
-  </si>
-  <si>
-    <t>images/NE.jpg</t>
-  </si>
-  <si>
-    <t>images/NI.jpg</t>
-  </si>
-  <si>
-    <t>images/DK.jpg</t>
-  </si>
-  <si>
-    <t>images/DO.jpg</t>
-  </si>
-  <si>
-    <t>images/DM.jpg</t>
-  </si>
-  <si>
-    <t>images/DE.jpg</t>
-  </si>
-  <si>
-    <t>images/TL.jpg</t>
-  </si>
-  <si>
-    <t>images/LA.jpg</t>
-  </si>
-  <si>
-    <t>images/LR.jpg</t>
-  </si>
-  <si>
-    <t>images/LV.jpg</t>
-  </si>
-  <si>
-    <t>images/RU.jpg</t>
-  </si>
-  <si>
-    <t>images/LB.jpg</t>
-  </si>
-  <si>
-    <t>images/LS.jpg</t>
-  </si>
-  <si>
-    <t>images/RE.jpg</t>
-  </si>
-  <si>
-    <t>images/RO.jpg</t>
-  </si>
-  <si>
-    <t>images/LU.jpg</t>
-  </si>
-  <si>
-    <t>images/RW.jpg</t>
-  </si>
-  <si>
-    <t>images/LY.jpg</t>
-  </si>
-  <si>
-    <t>images/LT.jpg</t>
-  </si>
-  <si>
-    <t>images/LI.jpg</t>
-  </si>
-  <si>
-    <t>images/MG.jpg</t>
-  </si>
-  <si>
-    <t>images/MQ.jpg</t>
-  </si>
-  <si>
-    <t>images/MH.jpg</t>
-  </si>
-  <si>
-    <t>images/YT.jpg</t>
-  </si>
-  <si>
-    <t>images/FM.jpg</t>
-  </si>
-  <si>
-    <t>images/MW.jpg</t>
-  </si>
-  <si>
-    <t>images/MY.jpg</t>
-  </si>
-  <si>
-    <t>images/ML.jpg</t>
-  </si>
-  <si>
-    <t>images/IM.jpg</t>
-  </si>
-  <si>
-    <t>images/MX.jpg</t>
-  </si>
-  <si>
-    <t>images/MC.jpg</t>
-  </si>
-  <si>
-    <t>images/MA.jpg</t>
-  </si>
-  <si>
-    <t>images/MU.jpg</t>
-  </si>
-  <si>
-    <t>images/MR.jpg</t>
-  </si>
-  <si>
-    <t>images/MZ.jpg</t>
-  </si>
-  <si>
-    <t>images/ME.jpg</t>
-  </si>
-  <si>
-    <t>images/MS.jpg</t>
-  </si>
-  <si>
-    <t>images/MD.jpg</t>
-  </si>
-  <si>
-    <t>images/MV.jpg</t>
-  </si>
-  <si>
-    <t>images/MT.jpg</t>
-  </si>
-  <si>
-    <t>images/MN.jpg</t>
-  </si>
-  <si>
-    <t>images/US.jpg</t>
-  </si>
-  <si>
-    <t>images/MM.jpg</t>
-  </si>
-  <si>
-    <t>images/VU.jpg</t>
-  </si>
-  <si>
-    <t>images/BH.jpg</t>
-  </si>
-  <si>
-    <t>images/BB.jpg</t>
-  </si>
-  <si>
-    <t>images/VA.jpg</t>
-  </si>
-  <si>
-    <t>images/BS.jpg</t>
-  </si>
-  <si>
-    <t>images/BD.jpg</t>
-  </si>
-  <si>
-    <t>images/BM.jpg</t>
-  </si>
-  <si>
-    <t>images/BJ.jpg</t>
-  </si>
-  <si>
-    <t>images/VE.jpg</t>
-  </si>
-  <si>
-    <t>images/VN.jpg</t>
-  </si>
-  <si>
-    <t>images/BE.jpg</t>
-  </si>
-  <si>
-    <t>images/BY.jpg</t>
-  </si>
-  <si>
-    <t>images/BZ.jpg</t>
-  </si>
-  <si>
-    <t>images/BA.jpg</t>
-  </si>
-  <si>
-    <t>images/BW.jpg</t>
-  </si>
-  <si>
-    <t>images/BO.jpg</t>
-  </si>
-  <si>
-    <t>images/BI.jpg</t>
-  </si>
-  <si>
-    <t>images/BF.jpg</t>
-  </si>
-  <si>
-    <t>images/BT.jpg</t>
-  </si>
-  <si>
-    <t>images/MP.jpg</t>
-  </si>
-  <si>
-    <t>images/MK.jpg</t>
-  </si>
-  <si>
-    <t>images/BG.jpg</t>
-  </si>
-  <si>
-    <t>images/BR.jpg</t>
-  </si>
-  <si>
-    <t>images/BN.jpg</t>
-  </si>
-  <si>
-    <t>images/WS.jpg</t>
-  </si>
-  <si>
-    <t>images/SA.jpg</t>
-  </si>
-  <si>
-    <t>images/CY.jpg</t>
-  </si>
-  <si>
-    <t>images/EH.jpg</t>
-  </si>
-  <si>
-    <t>images/SM.jpg</t>
-  </si>
-  <si>
-    <t>images/ST.jpg</t>
-  </si>
-  <si>
-    <t>images/PM.jpg</t>
-  </si>
-  <si>
-    <t>images/SN.jpg</t>
-  </si>
-  <si>
-    <t>images/RS.jpg</t>
-  </si>
-  <si>
-    <t>images/SC.jpg</t>
-  </si>
-  <si>
-    <t>images/LC.jpg</t>
-  </si>
-  <si>
-    <t>images/VC.jpg</t>
-  </si>
-  <si>
-    <t>images/KN.jpg</t>
-  </si>
-  <si>
-    <t>images/SH.jpg</t>
-  </si>
-  <si>
-    <t>images/SO.jpg</t>
-  </si>
-  <si>
-    <t>images/SB.jpg</t>
-  </si>
-  <si>
-    <t>images/SD.jpg</t>
-  </si>
-  <si>
-    <t>images/SR.jpg</t>
-  </si>
-  <si>
-    <t>images/LK.jpg</t>
-  </si>
-  <si>
-    <t>images/SE.jpg</t>
-  </si>
-  <si>
-    <t>images/CH.jpg</t>
-  </si>
-  <si>
-    <t>images/ES.jpg</t>
-  </si>
-  <si>
-    <t>images/SK.jpg</t>
-  </si>
-  <si>
-    <t>images/SI.jpg</t>
-  </si>
-  <si>
-    <t>images/SY.jpg</t>
-  </si>
-  <si>
-    <t>images/SL.jpg</t>
-  </si>
-  <si>
-    <t>images/SG.jpg</t>
-  </si>
-  <si>
-    <t>images/AE.jpg</t>
-  </si>
-  <si>
-    <t>images/AW.jpg</t>
-  </si>
-  <si>
-    <t>images/AM.jpg</t>
-  </si>
-  <si>
-    <t>images/AR.jpg</t>
-  </si>
-  <si>
-    <t>images/IS.jpg</t>
-  </si>
-  <si>
-    <t>images/HT.jpg</t>
-  </si>
-  <si>
-    <t>images/IE.jpg</t>
-  </si>
-  <si>
-    <t>images/AZ.jpg</t>
-  </si>
-  <si>
-    <t>images/AF.jpg</t>
-  </si>
-  <si>
-    <t>images/AD.jpg</t>
-  </si>
-  <si>
-    <t>images/AL.jpg</t>
-  </si>
-  <si>
-    <t>images/DZ.jpg</t>
-  </si>
-  <si>
-    <t>images/AO.jpg</t>
-  </si>
-  <si>
-    <t>images/AG.jpg</t>
-  </si>
-  <si>
-    <t>images/AI.jpg</t>
-  </si>
-  <si>
-    <t>images/ER.jpg</t>
-  </si>
-  <si>
-    <t>images/SZ.jpg</t>
-  </si>
-  <si>
-    <t>images/EE.jpg</t>
-  </si>
-  <si>
-    <t>images/EC.jpg</t>
-  </si>
-  <si>
-    <t>images/ET.jpg</t>
-  </si>
-  <si>
-    <t>images/SV.jpg</t>
-  </si>
-  <si>
-    <t>images/GB.jpg</t>
-  </si>
-  <si>
-    <t>images/AQ.jpg</t>
-  </si>
-  <si>
-    <t>images/VG.jpg</t>
-  </si>
-  <si>
-    <t>images/IO.jpg</t>
-  </si>
-  <si>
-    <t>images/YE.jpg</t>
-  </si>
-  <si>
-    <t>images/OM.jpg</t>
-  </si>
-  <si>
-    <t>images/AT.jpg</t>
-  </si>
-  <si>
-    <t>images/HN.jpg</t>
-  </si>
-  <si>
-    <t>images/WF.jpg</t>
-  </si>
-  <si>
-    <t>images/JO.jpg</t>
-  </si>
-  <si>
-    <t>images/UG.jpg</t>
-  </si>
-  <si>
-    <t>images/UY.jpg</t>
-  </si>
-  <si>
-    <t>images/UZ.jpg</t>
-  </si>
-  <si>
-    <t>images/UA.jpg</t>
-  </si>
-  <si>
-    <t>images/IQ.jpg</t>
-  </si>
-  <si>
-    <t>images/IR.jpg</t>
-  </si>
-  <si>
-    <t>images/IL.jpg</t>
-  </si>
-  <si>
-    <t>images/EG.jpg</t>
-  </si>
-  <si>
-    <t>images/IT.jpg</t>
-  </si>
-  <si>
-    <t>images/IN.jpg</t>
-  </si>
-  <si>
-    <t>images/ID.jpg</t>
-  </si>
-  <si>
-    <t>images/JP.jpg</t>
-  </si>
-  <si>
-    <t>images/JM.jpg</t>
-  </si>
-  <si>
-    <t>images/ZM.jpg</t>
-  </si>
-  <si>
-    <t>images/JE.jpg</t>
-  </si>
-  <si>
-    <t>images/GQ.jpg</t>
-  </si>
-  <si>
-    <t>images/GE.jpg</t>
-  </si>
-  <si>
-    <t>images/CN.jpg</t>
-  </si>
-  <si>
-    <t>images/CF.jpg</t>
-  </si>
-  <si>
-    <t>images/DJ.jpg</t>
-  </si>
-  <si>
-    <t>images/GI.jpg</t>
-  </si>
-  <si>
-    <t>images/ZW.jpg</t>
-  </si>
-  <si>
-    <t>images/TD.jpg</t>
-  </si>
-  <si>
-    <t>images/CZ.jpg</t>
-  </si>
-  <si>
-    <t>images/CL.jpg</t>
-  </si>
-  <si>
-    <t>images/CM.jpg</t>
-  </si>
-  <si>
-    <t>images/CV.jpg</t>
-  </si>
-  <si>
-    <t>images/KZ.jpg</t>
-  </si>
-  <si>
-    <t>images/QA.jpg</t>
+    <t>images/GH.gif</t>
+  </si>
+  <si>
+    <t>images/GA.gif</t>
+  </si>
+  <si>
+    <t>images/GY.gif</t>
+  </si>
+  <si>
+    <t>images/GM.gif</t>
+  </si>
+  <si>
+    <t>images/GG.gif</t>
+  </si>
+  <si>
+    <t>images/GP.gif</t>
+  </si>
+  <si>
+    <t>images/GT.gif</t>
+  </si>
+  <si>
+    <t>images/GU.gif</t>
+  </si>
+  <si>
+    <t>images/GD.gif</t>
+  </si>
+  <si>
+    <t>images/GR.gif</t>
+  </si>
+  <si>
+    <t>images/GL.gif</t>
+  </si>
+  <si>
+    <t>images/GN.gif</t>
+  </si>
+  <si>
+    <t>images/GW.gif</t>
+  </si>
+  <si>
+    <t>images/NA.gif</t>
+  </si>
+  <si>
+    <t>images/NR.gif</t>
+  </si>
+  <si>
+    <t>images/NG.gif</t>
+  </si>
+  <si>
+    <t>images/SS.gif</t>
+  </si>
+  <si>
+    <t>images/ZA.gif</t>
+  </si>
+  <si>
+    <t>images/NL.gif</t>
+  </si>
+  <si>
+    <t>images/AN.gif</t>
+  </si>
+  <si>
+    <t>images/NP.gif</t>
+  </si>
+  <si>
+    <t>images/NO.gif</t>
+  </si>
+  <si>
+    <t>images/NC.gif</t>
+  </si>
+  <si>
+    <t>images/NZ.gif</t>
+  </si>
+  <si>
+    <t>images/NU.gif</t>
+  </si>
+  <si>
+    <t>images/NE.gif</t>
+  </si>
+  <si>
+    <t>images/NI.gif</t>
+  </si>
+  <si>
+    <t>images/DK.gif</t>
+  </si>
+  <si>
+    <t>images/DM.gif</t>
+  </si>
+  <si>
+    <t>images/DE.gif</t>
+  </si>
+  <si>
+    <t>images/TL.gif</t>
+  </si>
+  <si>
+    <t>images/LA.gif</t>
+  </si>
+  <si>
+    <t>images/LR.gif</t>
+  </si>
+  <si>
+    <t>images/LV.gif</t>
+  </si>
+  <si>
+    <t>images/RU.gif</t>
+  </si>
+  <si>
+    <t>images/LB.gif</t>
+  </si>
+  <si>
+    <t>images/LS.gif</t>
+  </si>
+  <si>
+    <t>images/RE.gif</t>
+  </si>
+  <si>
+    <t>images/RO.gif</t>
+  </si>
+  <si>
+    <t>images/LU.gif</t>
+  </si>
+  <si>
+    <t>images/RW.gif</t>
+  </si>
+  <si>
+    <t>images/LY.gif</t>
+  </si>
+  <si>
+    <t>images/LT.gif</t>
+  </si>
+  <si>
+    <t>images/LI.gif</t>
+  </si>
+  <si>
+    <t>images/MG.gif</t>
+  </si>
+  <si>
+    <t>images/MQ.gif</t>
+  </si>
+  <si>
+    <t>images/MH.gif</t>
+  </si>
+  <si>
+    <t>images/YT.gif</t>
+  </si>
+  <si>
+    <t>images/FM.gif</t>
+  </si>
+  <si>
+    <t>images/MW.gif</t>
+  </si>
+  <si>
+    <t>images/MY.gif</t>
+  </si>
+  <si>
+    <t>images/ML.gif</t>
+  </si>
+  <si>
+    <t>images/IM.gif</t>
+  </si>
+  <si>
+    <t>images/MX.gif</t>
+  </si>
+  <si>
+    <t>images/MC.gif</t>
+  </si>
+  <si>
+    <t>images/MA.gif</t>
+  </si>
+  <si>
+    <t>images/MU.gif</t>
+  </si>
+  <si>
+    <t>images/MR.gif</t>
+  </si>
+  <si>
+    <t>images/MZ.gif</t>
+  </si>
+  <si>
+    <t>images/ME.gif</t>
+  </si>
+  <si>
+    <t>images/MS.gif</t>
+  </si>
+  <si>
+    <t>images/MD.gif</t>
+  </si>
+  <si>
+    <t>images/MV.gif</t>
+  </si>
+  <si>
+    <t>images/MT.gif</t>
+  </si>
+  <si>
+    <t>images/MN.gif</t>
+  </si>
+  <si>
+    <t>images/US.gif</t>
+  </si>
+  <si>
+    <t>images/MM.gif</t>
+  </si>
+  <si>
+    <t>images/VU.gif</t>
+  </si>
+  <si>
+    <t>images/BH.gif</t>
+  </si>
+  <si>
+    <t>images/BB.gif</t>
+  </si>
+  <si>
+    <t>images/VA.gif</t>
+  </si>
+  <si>
+    <t>images/BS.gif</t>
+  </si>
+  <si>
+    <t>images/BD.gif</t>
+  </si>
+  <si>
+    <t>images/BM.gif</t>
+  </si>
+  <si>
+    <t>images/BJ.gif</t>
+  </si>
+  <si>
+    <t>images/VE.gif</t>
+  </si>
+  <si>
+    <t>images/VN.gif</t>
+  </si>
+  <si>
+    <t>images/BE.gif</t>
+  </si>
+  <si>
+    <t>images/BY.gif</t>
+  </si>
+  <si>
+    <t>images/BZ.gif</t>
+  </si>
+  <si>
+    <t>images/BA.gif</t>
+  </si>
+  <si>
+    <t>images/BW.gif</t>
+  </si>
+  <si>
+    <t>images/BO.gif</t>
+  </si>
+  <si>
+    <t>images/BI.gif</t>
+  </si>
+  <si>
+    <t>images/BF.gif</t>
+  </si>
+  <si>
+    <t>images/BT.gif</t>
+  </si>
+  <si>
+    <t>images/MP.gif</t>
+  </si>
+  <si>
+    <t>images/MK.gif</t>
+  </si>
+  <si>
+    <t>images/BG.gif</t>
+  </si>
+  <si>
+    <t>images/BR.gif</t>
+  </si>
+  <si>
+    <t>images/BN.gif</t>
+  </si>
+  <si>
+    <t>images/WS.gif</t>
+  </si>
+  <si>
+    <t>images/SA.gif</t>
+  </si>
+  <si>
+    <t>images/CY.gif</t>
+  </si>
+  <si>
+    <t>images/EH.gif</t>
+  </si>
+  <si>
+    <t>images/SM.gif</t>
+  </si>
+  <si>
+    <t>images/ST.gif</t>
+  </si>
+  <si>
+    <t>images/PM.gif</t>
+  </si>
+  <si>
+    <t>images/SN.gif</t>
+  </si>
+  <si>
+    <t>images/RS.gif</t>
+  </si>
+  <si>
+    <t>images/SC.gif</t>
+  </si>
+  <si>
+    <t>images/VC.gif</t>
+  </si>
+  <si>
+    <t>images/KN.gif</t>
+  </si>
+  <si>
+    <t>images/SH.gif</t>
+  </si>
+  <si>
+    <t>images/SO.gif</t>
+  </si>
+  <si>
+    <t>images/SB.gif</t>
+  </si>
+  <si>
+    <t>images/SD.gif</t>
+  </si>
+  <si>
+    <t>images/SR.gif</t>
+  </si>
+  <si>
+    <t>images/LK.gif</t>
+  </si>
+  <si>
+    <t>images/SE.gif</t>
+  </si>
+  <si>
+    <t>images/CH.gif</t>
+  </si>
+  <si>
+    <t>images/ES.gif</t>
+  </si>
+  <si>
+    <t>images/SK.gif</t>
+  </si>
+  <si>
+    <t>images/SI.gif</t>
+  </si>
+  <si>
+    <t>images/SY.gif</t>
+  </si>
+  <si>
+    <t>images/SL.gif</t>
+  </si>
+  <si>
+    <t>images/SG.gif</t>
+  </si>
+  <si>
+    <t>images/AE.gif</t>
+  </si>
+  <si>
+    <t>images/AW.gif</t>
+  </si>
+  <si>
+    <t>images/AM.gif</t>
+  </si>
+  <si>
+    <t>images/AR.gif</t>
+  </si>
+  <si>
+    <t>images/IS.gif</t>
+  </si>
+  <si>
+    <t>images/HT.gif</t>
+  </si>
+  <si>
+    <t>images/IE.gif</t>
+  </si>
+  <si>
+    <t>images/AZ.gif</t>
+  </si>
+  <si>
+    <t>images/AF.gif</t>
+  </si>
+  <si>
+    <t>images/AD.gif</t>
+  </si>
+  <si>
+    <t>images/AL.gif</t>
+  </si>
+  <si>
+    <t>images/DZ.gif</t>
+  </si>
+  <si>
+    <t>images/AO.gif</t>
+  </si>
+  <si>
+    <t>images/AG.gif</t>
+  </si>
+  <si>
+    <t>images/AI.gif</t>
+  </si>
+  <si>
+    <t>images/ER.gif</t>
+  </si>
+  <si>
+    <t>images/SZ.gif</t>
+  </si>
+  <si>
+    <t>images/EE.gif</t>
+  </si>
+  <si>
+    <t>images/EC.gif</t>
+  </si>
+  <si>
+    <t>images/ET.gif</t>
+  </si>
+  <si>
+    <t>images/GB.gif</t>
+  </si>
+  <si>
+    <t>images/AQ.gif</t>
+  </si>
+  <si>
+    <t>images/VG.gif</t>
+  </si>
+  <si>
+    <t>images/IO.gif</t>
+  </si>
+  <si>
+    <t>images/YE.gif</t>
+  </si>
+  <si>
+    <t>images/OM.gif</t>
+  </si>
+  <si>
+    <t>images/AT.gif</t>
+  </si>
+  <si>
+    <t>images/HN.gif</t>
+  </si>
+  <si>
+    <t>images/WF.gif</t>
+  </si>
+  <si>
+    <t>images/JO.gif</t>
+  </si>
+  <si>
+    <t>images/UG.gif</t>
+  </si>
+  <si>
+    <t>images/UY.gif</t>
+  </si>
+  <si>
+    <t>images/UZ.gif</t>
+  </si>
+  <si>
+    <t>images/UA.gif</t>
+  </si>
+  <si>
+    <t>images/IQ.gif</t>
+  </si>
+  <si>
+    <t>images/IR.gif</t>
+  </si>
+  <si>
+    <t>images/IL.gif</t>
+  </si>
+  <si>
+    <t>images/EG.gif</t>
+  </si>
+  <si>
+    <t>images/IT.gif</t>
+  </si>
+  <si>
+    <t>images/IN.gif</t>
+  </si>
+  <si>
+    <t>images/ID.gif</t>
+  </si>
+  <si>
+    <t>images/JP.gif</t>
+  </si>
+  <si>
+    <t>images/JM.gif</t>
+  </si>
+  <si>
+    <t>images/ZM.gif</t>
+  </si>
+  <si>
+    <t>images/JE.gif</t>
+  </si>
+  <si>
+    <t>images/GQ.gif</t>
+  </si>
+  <si>
+    <t>images/GE.gif</t>
+  </si>
+  <si>
+    <t>images/CN.gif</t>
+  </si>
+  <si>
+    <t>images/CF.gif</t>
+  </si>
+  <si>
+    <t>images/DJ.gif</t>
+  </si>
+  <si>
+    <t>images/GI.gif</t>
+  </si>
+  <si>
+    <t>images/ZW.gif</t>
+  </si>
+  <si>
+    <t>images/TD.gif</t>
+  </si>
+  <si>
+    <t>images/CZ.gif</t>
+  </si>
+  <si>
+    <t>images/CL.gif</t>
+  </si>
+  <si>
+    <t>images/CM.gif</t>
+  </si>
+  <si>
+    <t>images/CV.gif</t>
+  </si>
+  <si>
+    <t>images/KZ.gif</t>
+  </si>
+  <si>
+    <t>images/QA.gif</t>
+  </si>
+  <si>
+    <t>images/CA.gif</t>
+  </si>
+  <si>
+    <t>images/KE.gif</t>
+  </si>
+  <si>
+    <t>images/KY.gif</t>
+  </si>
+  <si>
+    <t>images/KM.gif</t>
+  </si>
+  <si>
+    <t>images/XK.gif</t>
+  </si>
+  <si>
+    <t>images/CR.gif</t>
+  </si>
+  <si>
+    <t>images/CI.gif</t>
+  </si>
+  <si>
+    <t>images/CO.gif</t>
+  </si>
+  <si>
+    <t>images/CG.gif</t>
+  </si>
+  <si>
+    <t>images/CD.gif</t>
+  </si>
+  <si>
+    <t>images/CU.gif</t>
+  </si>
+  <si>
+    <t>images/KW.gif</t>
+  </si>
+  <si>
+    <t>images/CK.gif</t>
+  </si>
+  <si>
+    <t>images/HR.gif</t>
+  </si>
+  <si>
+    <t>images/KG.gif</t>
+  </si>
+  <si>
+    <t>images/KI.gif</t>
+  </si>
+  <si>
+    <t>images/TW.gif</t>
+  </si>
+  <si>
+    <t>images/TJ.gif</t>
+  </si>
+  <si>
+    <t>images/TZ.gif</t>
+  </si>
+  <si>
+    <t>images/TH.gif</t>
+  </si>
+  <si>
+    <t>images/TC.gif</t>
+  </si>
+  <si>
+    <t>images/TR.gif</t>
+  </si>
+  <si>
+    <t>images/TG.gif</t>
+  </si>
+  <si>
+    <t>images/TO.gif</t>
+  </si>
+  <si>
+    <t>images/TM.gif</t>
+  </si>
+  <si>
+    <t>images/TV.gif</t>
+  </si>
+  <si>
+    <t>images/TN.gif</t>
+  </si>
+  <si>
+    <t>images/TT.gif</t>
+  </si>
+  <si>
+    <t>images/PA.gif</t>
+  </si>
+  <si>
+    <t>images/PY.gif</t>
+  </si>
+  <si>
+    <t>images/PK.gif</t>
+  </si>
+  <si>
+    <t>images/PG.gif</t>
+  </si>
+  <si>
+    <t>images/PW.gif</t>
+  </si>
+  <si>
+    <t>images/PS.gif</t>
+  </si>
+  <si>
+    <t>images/PE.gif</t>
+  </si>
+  <si>
+    <t>images/PT.gif</t>
+  </si>
+  <si>
+    <t>images/PL.gif</t>
+  </si>
+  <si>
+    <t>images/FR.gif</t>
+  </si>
+  <si>
+    <t>images/GF.gif</t>
+  </si>
+  <si>
+    <t>images/PF.gif</t>
+  </si>
+  <si>
+    <t>images/FJ.gif</t>
+  </si>
+  <si>
+    <t>images/FI.gif</t>
+  </si>
+  <si>
+    <t>images/PH.gif</t>
+  </si>
+  <si>
+    <t>images/PN.gif</t>
+  </si>
+  <si>
+    <t>images/HU.gif</t>
+  </si>
+  <si>
+    <t>images/AU.gif</t>
   </si>
   <si>
     <t>images/KH.jpg</t>
-  </si>
-  <si>
-    <t>images/CA.jpg</t>
-  </si>
-  <si>
-    <t>images/KE.jpg</t>
-  </si>
-  <si>
-    <t>images/KY.jpg</t>
-  </si>
-  <si>
-    <t>images/KM.jpg</t>
-  </si>
-  <si>
-    <t>images/XK.jpg</t>
-  </si>
-  <si>
-    <t>images/CR.jpg</t>
-  </si>
-  <si>
-    <t>images/CI.jpg</t>
-  </si>
-  <si>
-    <t>images/CO.jpg</t>
-  </si>
-  <si>
-    <t>images/CG.jpg</t>
-  </si>
-  <si>
-    <t>images/CD.jpg</t>
-  </si>
-  <si>
-    <t>images/CU.jpg</t>
-  </si>
-  <si>
-    <t>images/KW.jpg</t>
-  </si>
-  <si>
-    <t>images/CK.jpg</t>
-  </si>
-  <si>
-    <t>images/HR.jpg</t>
-  </si>
-  <si>
-    <t>images/KG.jpg</t>
-  </si>
-  <si>
-    <t>images/KI.jpg</t>
-  </si>
-  <si>
-    <t>images/TW.jpg</t>
-  </si>
-  <si>
-    <t>images/TJ.jpg</t>
-  </si>
-  <si>
-    <t>images/TZ.jpg</t>
-  </si>
-  <si>
-    <t>images/TH.jpg</t>
-  </si>
-  <si>
-    <t>images/TC.jpg</t>
-  </si>
-  <si>
-    <t>images/TR.jpg</t>
-  </si>
-  <si>
-    <t>images/TG.jpg</t>
-  </si>
-  <si>
-    <t>images/TO.jpg</t>
-  </si>
-  <si>
-    <t>images/TM.jpg</t>
-  </si>
-  <si>
-    <t>images/TV.jpg</t>
-  </si>
-  <si>
-    <t>images/TN.jpg</t>
-  </si>
-  <si>
-    <t>images/TT.jpg</t>
-  </si>
-  <si>
-    <t>images/PA.jpg</t>
-  </si>
-  <si>
-    <t>images/PY.jpg</t>
-  </si>
-  <si>
-    <t>images/PK.jpg</t>
-  </si>
-  <si>
-    <t>images/PG.jpg</t>
-  </si>
-  <si>
-    <t>images/PW.jpg</t>
-  </si>
-  <si>
-    <t>images/PS.jpg</t>
-  </si>
-  <si>
-    <t>images/PE.jpg</t>
-  </si>
-  <si>
-    <t>images/PT.jpg</t>
-  </si>
-  <si>
-    <t>images/PL.jpg</t>
-  </si>
-  <si>
-    <t>images/FR.jpg</t>
-  </si>
-  <si>
-    <t>images/GF.jpg</t>
-  </si>
-  <si>
-    <t>images/PF.jpg</t>
-  </si>
-  <si>
-    <t>images/FJ.jpg</t>
-  </si>
-  <si>
-    <t>images/FI.jpg</t>
-  </si>
-  <si>
-    <t>images/PH.jpg</t>
-  </si>
-  <si>
-    <t>images/PN.jpg</t>
-  </si>
-  <si>
-    <t>images/HU.jpg</t>
-  </si>
-  <si>
-    <t>images/AU.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/SV.bmp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/LC.bmp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/DO.bmp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2765,7 +2769,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>326</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -2773,7 +2777,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -2781,7 +2785,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -2789,7 +2793,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -2797,7 +2801,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -2805,7 +2809,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -2813,7 +2817,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -2821,7 +2825,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -2829,7 +2833,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -2837,7 +2841,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -2845,7 +2849,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -2853,7 +2857,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -2861,7 +2865,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -2869,7 +2873,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
@@ -2877,7 +2881,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
@@ -2885,7 +2889,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -2893,7 +2897,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
@@ -2901,7 +2905,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -2909,7 +2913,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
@@ -2917,7 +2921,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
@@ -2925,7 +2929,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -2933,7 +2937,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
@@ -2941,7 +2945,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
@@ -2949,7 +2953,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
@@ -2957,7 +2961,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
@@ -2965,7 +2969,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -2973,7 +2977,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -2981,7 +2985,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -2989,7 +2993,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
@@ -2997,7 +3001,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -3005,7 +3009,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
@@ -3013,7 +3017,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
@@ -3021,7 +3025,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
@@ -3029,7 +3033,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3037,7 +3041,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
@@ -3045,7 +3049,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -3053,7 +3057,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -3061,7 +3065,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
@@ -3069,7 +3073,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
@@ -3077,7 +3081,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
@@ -3085,7 +3089,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
@@ -3093,7 +3097,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
@@ -3101,7 +3105,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
@@ -3109,7 +3113,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
@@ -3117,7 +3121,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
@@ -3125,7 +3129,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
@@ -3133,7 +3137,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
@@ -3141,7 +3145,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
@@ -3149,7 +3153,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
@@ -3157,7 +3161,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
@@ -3165,7 +3169,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
@@ -3173,7 +3177,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
@@ -3181,7 +3185,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
@@ -3189,7 +3193,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
@@ -3197,7 +3201,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
@@ -3205,7 +3209,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
@@ -3213,7 +3217,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
@@ -3221,7 +3225,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
@@ -3229,7 +3233,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
@@ -3237,7 +3241,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
@@ -3245,7 +3249,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
@@ -3253,7 +3257,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
@@ -3261,7 +3265,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
@@ -3269,7 +3273,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
@@ -3277,7 +3281,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
@@ -3285,7 +3289,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
@@ -3293,7 +3297,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
@@ -3301,7 +3305,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
@@ -3309,7 +3313,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
@@ -3317,7 +3321,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
@@ -3325,7 +3329,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
@@ -3333,7 +3337,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
@@ -3341,7 +3345,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
@@ -3349,7 +3353,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
@@ -3357,7 +3361,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>400</v>
+        <v>522</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
@@ -3365,7 +3369,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
@@ -3373,7 +3377,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
@@ -3381,7 +3385,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
@@ -3389,7 +3393,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
@@ -3397,7 +3401,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
@@ -3405,7 +3409,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
@@ -3413,7 +3417,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
@@ -3421,7 +3425,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
@@ -3429,7 +3433,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
@@ -3437,7 +3441,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
@@ -3445,7 +3449,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
@@ -3453,7 +3457,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
@@ -3461,7 +3465,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
@@ -3469,7 +3473,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
@@ -3477,7 +3481,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
@@ -3485,7 +3489,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
@@ -3493,7 +3497,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
@@ -3501,7 +3505,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
@@ -3509,7 +3513,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
@@ -3517,7 +3521,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
@@ -3525,7 +3529,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
@@ -3533,7 +3537,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
@@ -3541,7 +3545,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
@@ -3549,7 +3553,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
@@ -3557,7 +3561,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
@@ -3565,7 +3569,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.3">
@@ -3573,7 +3577,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
@@ -3581,7 +3585,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
@@ -3589,7 +3593,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.3">
@@ -3597,7 +3601,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.3">
@@ -3605,7 +3609,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.3">
@@ -3613,7 +3617,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
@@ -3621,7 +3625,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
@@ -3629,7 +3633,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.3">
@@ -3637,7 +3641,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.3">
@@ -3645,7 +3649,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
@@ -3653,7 +3657,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>437</v>
+        <v>521</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
@@ -3661,7 +3665,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.3">
@@ -3669,7 +3673,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.3">
@@ -3677,7 +3681,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.3">
@@ -3685,7 +3689,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.3">
@@ -3693,7 +3697,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.3">
@@ -3701,7 +3705,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.3">
@@ -3709,7 +3713,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
@@ -3717,7 +3721,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.3">
@@ -3725,7 +3729,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.3">
@@ -3733,7 +3737,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
@@ -3741,7 +3745,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
@@ -3749,7 +3753,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
@@ -3757,7 +3761,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
@@ -3765,7 +3769,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
@@ -3773,7 +3777,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.3">
@@ -3781,7 +3785,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.3">
@@ -3789,7 +3793,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.3">
@@ -3797,7 +3801,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.3">
@@ -3805,7 +3809,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.3">
@@ -3813,7 +3817,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
@@ -3821,7 +3825,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
@@ -3829,7 +3833,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.3">
@@ -3837,7 +3841,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
@@ -3845,7 +3849,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
@@ -3853,7 +3857,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.3">
@@ -3861,7 +3865,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.3">
@@ -3869,7 +3873,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.3">
@@ -3877,7 +3881,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.3">
@@ -3885,7 +3889,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.3">
@@ -3893,7 +3897,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.3">
@@ -3901,7 +3905,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.3">
@@ -3909,7 +3913,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
@@ -3917,7 +3921,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
@@ -3925,7 +3929,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.3">
@@ -3933,7 +3937,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
@@ -3941,7 +3945,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
@@ -3949,7 +3953,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
@@ -3957,7 +3961,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.3">
@@ -3965,7 +3969,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.3">
@@ -3973,7 +3977,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.3">
@@ -3981,7 +3985,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.3">
@@ -3989,7 +3993,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.3">
@@ -3997,7 +4001,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.3">
@@ -4005,7 +4009,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.3">
@@ -4013,7 +4017,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.3">
@@ -4021,7 +4025,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.3">
@@ -4029,7 +4033,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
@@ -4037,7 +4041,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
@@ -4045,7 +4049,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.3">
@@ -4053,7 +4057,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
@@ -4061,7 +4065,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.3">
@@ -4069,7 +4073,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.3">
@@ -4077,7 +4081,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.3">
@@ -4085,7 +4089,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.3">
@@ -4093,7 +4097,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.3">
@@ -4101,7 +4105,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.3">
@@ -4109,7 +4113,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.3">
@@ -4117,7 +4121,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.3">
@@ -4125,7 +4129,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.3">
@@ -4133,7 +4137,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.3">
@@ -4141,7 +4145,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.3">
@@ -4149,7 +4153,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.3">
@@ -4157,7 +4161,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.3">
@@ -4165,7 +4169,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.3">
@@ -4173,7 +4177,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.3">
@@ -4181,7 +4185,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.3">
@@ -4189,7 +4193,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.3">
@@ -4197,7 +4201,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.3">
@@ -4205,7 +4209,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.3">
@@ -4213,7 +4217,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.3">
@@ -4221,7 +4225,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.3">
@@ -4229,7 +4233,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.3">
@@ -4237,7 +4241,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.3">
@@ -4245,7 +4249,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.3">
@@ -4253,7 +4257,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.3">
@@ -4261,7 +4265,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.3">
@@ -4269,7 +4273,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.3">
@@ -4277,7 +4281,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.3">
@@ -4285,7 +4289,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.3">
@@ -4293,7 +4297,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.3">
@@ -4301,7 +4305,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.3">
@@ -4309,7 +4313,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.3">
@@ -4317,7 +4321,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.3">
@@ -4325,7 +4329,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
@@ -4333,7 +4337,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -4341,7 +4345,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">

--- a/flash.xlsx
+++ b/flash.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
   <si>
     <t>가나</t>
   </si>
@@ -30,27 +30,15 @@
     <t>감비아</t>
   </si>
   <si>
-    <t>건지</t>
-  </si>
-  <si>
-    <t>과들루프</t>
-  </si>
-  <si>
     <t>과테말라</t>
   </si>
   <si>
-    <t>괌</t>
-  </si>
-  <si>
     <t>그레나다</t>
   </si>
   <si>
     <t>그리스</t>
   </si>
   <si>
-    <t>그린란드</t>
-  </si>
-  <si>
     <t>기니</t>
   </si>
   <si>
@@ -75,24 +63,15 @@
     <t>네덜란드</t>
   </si>
   <si>
-    <t>네덜란드령 안틸레스</t>
-  </si>
-  <si>
     <t>네팔</t>
   </si>
   <si>
     <t>노르웨이</t>
   </si>
   <si>
-    <t>뉴 칼레도니아</t>
-  </si>
-  <si>
     <t>뉴질랜드</t>
   </si>
   <si>
-    <t>니우에</t>
-  </si>
-  <si>
     <t>니제르</t>
   </si>
   <si>
@@ -132,9 +111,6 @@
     <t>레소토</t>
   </si>
   <si>
-    <t>레위니옹</t>
-  </si>
-  <si>
     <t>루마니아</t>
   </si>
   <si>
@@ -156,15 +132,9 @@
     <t>마다가스카르</t>
   </si>
   <si>
-    <t>마르티니크</t>
-  </si>
-  <si>
     <t>마셜제도</t>
   </si>
   <si>
-    <t>마요트</t>
-  </si>
-  <si>
     <t>마이크로네시아연방</t>
   </si>
   <si>
@@ -177,9 +147,6 @@
     <t>말리</t>
   </si>
   <si>
-    <t>맨 섬</t>
-  </si>
-  <si>
     <t>멕시코</t>
   </si>
   <si>
@@ -201,9 +168,6 @@
     <t>몬테네그로</t>
   </si>
   <si>
-    <t>몬트세랫</t>
-  </si>
-  <si>
     <t>몰도바</t>
   </si>
   <si>
@@ -240,9 +204,6 @@
     <t>방글라데시</t>
   </si>
   <si>
-    <t>버뮤다</t>
-  </si>
-  <si>
     <t>베냉</t>
   </si>
   <si>
@@ -279,9 +240,6 @@
     <t>부탄</t>
   </si>
   <si>
-    <t>북마리아나 군도</t>
-  </si>
-  <si>
     <t>북마케도니아</t>
   </si>
   <si>
@@ -303,18 +261,12 @@
     <t>사이프러스</t>
   </si>
   <si>
-    <t>사하라 아랍민주공화국(서부사하라)</t>
-  </si>
-  <si>
     <t>산마리노</t>
   </si>
   <si>
     <t>상투메프린시페</t>
   </si>
   <si>
-    <t>생피에르·미클롱</t>
-  </si>
-  <si>
     <t>세네갈</t>
   </si>
   <si>
@@ -333,9 +285,6 @@
     <t>세인트 키츠 네비스</t>
   </si>
   <si>
-    <t>세인트 헬레나 섬</t>
-  </si>
-  <si>
     <t>소말리아</t>
   </si>
   <si>
@@ -378,9 +327,6 @@
     <t>아랍에미리트</t>
   </si>
   <si>
-    <t>아루바</t>
-  </si>
-  <si>
     <t>아르메니아</t>
   </si>
   <si>
@@ -417,9 +363,6 @@
     <t>앤티가바부다</t>
   </si>
   <si>
-    <t>앵귈라</t>
-  </si>
-  <si>
     <t>에리트레아</t>
   </si>
   <si>
@@ -441,15 +384,6 @@
     <t>영국</t>
   </si>
   <si>
-    <t>영국령 남극지역</t>
-  </si>
-  <si>
-    <t>영국령 버진 아일랜드</t>
-  </si>
-  <si>
-    <t>영국령 인도양 제도</t>
-  </si>
-  <si>
     <t>예멘</t>
   </si>
   <si>
@@ -462,9 +396,6 @@
     <t>온두라스</t>
   </si>
   <si>
-    <t>왈리스·퓌튀나</t>
-  </si>
-  <si>
     <t>요르단</t>
   </si>
   <si>
@@ -510,9 +441,6 @@
     <t>잠비아</t>
   </si>
   <si>
-    <t>저지</t>
-  </si>
-  <si>
     <t>적도기니</t>
   </si>
   <si>
@@ -528,9 +456,6 @@
     <t>지부티</t>
   </si>
   <si>
-    <t>지브롤터</t>
-  </si>
-  <si>
     <t>짐바브웨</t>
   </si>
   <si>
@@ -561,12 +486,6 @@
     <t>캐나다</t>
   </si>
   <si>
-    <t>케냐</t>
-  </si>
-  <si>
-    <t>케이맨제도</t>
-  </si>
-  <si>
     <t>코모로</t>
   </si>
   <si>
@@ -606,9 +525,6 @@
     <t>키리바시</t>
   </si>
   <si>
-    <t>타이완</t>
-  </si>
-  <si>
     <t>타지키스탄</t>
   </si>
   <si>
@@ -618,9 +534,6 @@
     <t>태국</t>
   </si>
   <si>
-    <t>터크스·케이커스 제도</t>
-  </si>
-  <si>
     <t>터키</t>
   </si>
   <si>
@@ -666,18 +579,9 @@
     <t>포르투갈</t>
   </si>
   <si>
-    <t>폴란드</t>
-  </si>
-  <si>
     <t>프랑스</t>
   </si>
   <si>
-    <t>프랑스령 기아나</t>
-  </si>
-  <si>
-    <t>프랑스령 폴리네시아</t>
-  </si>
-  <si>
     <t>피지</t>
   </si>
   <si>
@@ -687,9 +591,6 @@
     <t>필리핀</t>
   </si>
   <si>
-    <t>핏케언 섬</t>
-  </si>
-  <si>
     <t>헝가리</t>
   </si>
   <si>
@@ -924,27 +825,15 @@
     <t>images/GM.gif</t>
   </si>
   <si>
-    <t>images/GG.gif</t>
-  </si>
-  <si>
-    <t>images/GP.gif</t>
-  </si>
-  <si>
     <t>images/GT.gif</t>
   </si>
   <si>
-    <t>images/GU.gif</t>
-  </si>
-  <si>
     <t>images/GD.gif</t>
   </si>
   <si>
     <t>images/GR.gif</t>
   </si>
   <si>
-    <t>images/GL.gif</t>
-  </si>
-  <si>
     <t>images/GN.gif</t>
   </si>
   <si>
@@ -969,24 +858,15 @@
     <t>images/NL.gif</t>
   </si>
   <si>
-    <t>images/AN.gif</t>
-  </si>
-  <si>
     <t>images/NP.gif</t>
   </si>
   <si>
     <t>images/NO.gif</t>
   </si>
   <si>
-    <t>images/NC.gif</t>
-  </si>
-  <si>
     <t>images/NZ.gif</t>
   </si>
   <si>
-    <t>images/NU.gif</t>
-  </si>
-  <si>
     <t>images/NE.gif</t>
   </si>
   <si>
@@ -1023,9 +903,6 @@
     <t>images/LS.gif</t>
   </si>
   <si>
-    <t>images/RE.gif</t>
-  </si>
-  <si>
     <t>images/RO.gif</t>
   </si>
   <si>
@@ -1047,15 +924,9 @@
     <t>images/MG.gif</t>
   </si>
   <si>
-    <t>images/MQ.gif</t>
-  </si>
-  <si>
     <t>images/MH.gif</t>
   </si>
   <si>
-    <t>images/YT.gif</t>
-  </si>
-  <si>
     <t>images/FM.gif</t>
   </si>
   <si>
@@ -1068,9 +939,6 @@
     <t>images/ML.gif</t>
   </si>
   <si>
-    <t>images/IM.gif</t>
-  </si>
-  <si>
     <t>images/MX.gif</t>
   </si>
   <si>
@@ -1092,9 +960,6 @@
     <t>images/ME.gif</t>
   </si>
   <si>
-    <t>images/MS.gif</t>
-  </si>
-  <si>
     <t>images/MD.gif</t>
   </si>
   <si>
@@ -1131,9 +996,6 @@
     <t>images/BD.gif</t>
   </si>
   <si>
-    <t>images/BM.gif</t>
-  </si>
-  <si>
     <t>images/BJ.gif</t>
   </si>
   <si>
@@ -1170,9 +1032,6 @@
     <t>images/BT.gif</t>
   </si>
   <si>
-    <t>images/MP.gif</t>
-  </si>
-  <si>
     <t>images/MK.gif</t>
   </si>
   <si>
@@ -1194,18 +1053,12 @@
     <t>images/CY.gif</t>
   </si>
   <si>
-    <t>images/EH.gif</t>
-  </si>
-  <si>
     <t>images/SM.gif</t>
   </si>
   <si>
     <t>images/ST.gif</t>
   </si>
   <si>
-    <t>images/PM.gif</t>
-  </si>
-  <si>
     <t>images/SN.gif</t>
   </si>
   <si>
@@ -1221,9 +1074,6 @@
     <t>images/KN.gif</t>
   </si>
   <si>
-    <t>images/SH.gif</t>
-  </si>
-  <si>
     <t>images/SO.gif</t>
   </si>
   <si>
@@ -1266,9 +1116,6 @@
     <t>images/AE.gif</t>
   </si>
   <si>
-    <t>images/AW.gif</t>
-  </si>
-  <si>
     <t>images/AM.gif</t>
   </si>
   <si>
@@ -1305,9 +1152,6 @@
     <t>images/AG.gif</t>
   </si>
   <si>
-    <t>images/AI.gif</t>
-  </si>
-  <si>
     <t>images/ER.gif</t>
   </si>
   <si>
@@ -1326,15 +1170,6 @@
     <t>images/GB.gif</t>
   </si>
   <si>
-    <t>images/AQ.gif</t>
-  </si>
-  <si>
-    <t>images/VG.gif</t>
-  </si>
-  <si>
-    <t>images/IO.gif</t>
-  </si>
-  <si>
     <t>images/YE.gif</t>
   </si>
   <si>
@@ -1347,9 +1182,6 @@
     <t>images/HN.gif</t>
   </si>
   <si>
-    <t>images/WF.gif</t>
-  </si>
-  <si>
     <t>images/JO.gif</t>
   </si>
   <si>
@@ -1395,9 +1227,6 @@
     <t>images/ZM.gif</t>
   </si>
   <si>
-    <t>images/JE.gif</t>
-  </si>
-  <si>
     <t>images/GQ.gif</t>
   </si>
   <si>
@@ -1413,9 +1242,6 @@
     <t>images/DJ.gif</t>
   </si>
   <si>
-    <t>images/GI.gif</t>
-  </si>
-  <si>
     <t>images/ZW.gif</t>
   </si>
   <si>
@@ -1443,12 +1269,6 @@
     <t>images/CA.gif</t>
   </si>
   <si>
-    <t>images/KE.gif</t>
-  </si>
-  <si>
-    <t>images/KY.gif</t>
-  </si>
-  <si>
     <t>images/KM.gif</t>
   </si>
   <si>
@@ -1488,9 +1308,6 @@
     <t>images/KI.gif</t>
   </si>
   <si>
-    <t>images/TW.gif</t>
-  </si>
-  <si>
     <t>images/TJ.gif</t>
   </si>
   <si>
@@ -1500,9 +1317,6 @@
     <t>images/TH.gif</t>
   </si>
   <si>
-    <t>images/TC.gif</t>
-  </si>
-  <si>
     <t>images/TR.gif</t>
   </si>
   <si>
@@ -1548,18 +1362,9 @@
     <t>images/PT.gif</t>
   </si>
   <si>
-    <t>images/PL.gif</t>
-  </si>
-  <si>
     <t>images/FR.gif</t>
   </si>
   <si>
-    <t>images/GF.gif</t>
-  </si>
-  <si>
-    <t>images/PF.gif</t>
-  </si>
-  <si>
     <t>images/FJ.gif</t>
   </si>
   <si>
@@ -1567,9 +1372,6 @@
   </si>
   <si>
     <t>images/PH.gif</t>
-  </si>
-  <si>
-    <t>images/PN.gif</t>
   </si>
   <si>
     <t>images/HU.gif</t>
@@ -1592,6 +1394,594 @@
   <si>
     <t>images/DO.bmp</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD.gif</t>
+  </si>
+  <si>
+    <t>AE.gif</t>
+  </si>
+  <si>
+    <t>AF.gif</t>
+  </si>
+  <si>
+    <t>AG.gif</t>
+  </si>
+  <si>
+    <t>AL.gif</t>
+  </si>
+  <si>
+    <t>AM.gif</t>
+  </si>
+  <si>
+    <t>AO.gif</t>
+  </si>
+  <si>
+    <t>AR.gif</t>
+  </si>
+  <si>
+    <t>AT.gif</t>
+  </si>
+  <si>
+    <t>AU.gif</t>
+  </si>
+  <si>
+    <t>AZ.gif</t>
+  </si>
+  <si>
+    <t>BA.gif</t>
+  </si>
+  <si>
+    <t>BB.gif</t>
+  </si>
+  <si>
+    <t>BD.gif</t>
+  </si>
+  <si>
+    <t>BE.gif</t>
+  </si>
+  <si>
+    <t>BF.gif</t>
+  </si>
+  <si>
+    <t>BG.gif</t>
+  </si>
+  <si>
+    <t>BH.gif</t>
+  </si>
+  <si>
+    <t>BI.gif</t>
+  </si>
+  <si>
+    <t>BJ.gif</t>
+  </si>
+  <si>
+    <t>BN.gif</t>
+  </si>
+  <si>
+    <t>BO.gif</t>
+  </si>
+  <si>
+    <t>BR.gif</t>
+  </si>
+  <si>
+    <t>BS.gif</t>
+  </si>
+  <si>
+    <t>BT.gif</t>
+  </si>
+  <si>
+    <t>BW.gif</t>
+  </si>
+  <si>
+    <t>BY.gif</t>
+  </si>
+  <si>
+    <t>BZ.gif</t>
+  </si>
+  <si>
+    <t>CA.gif</t>
+  </si>
+  <si>
+    <t>CD.gif</t>
+  </si>
+  <si>
+    <t>CF.gif</t>
+  </si>
+  <si>
+    <t>CG.gif</t>
+  </si>
+  <si>
+    <t>CH.gif</t>
+  </si>
+  <si>
+    <t>CI.gif</t>
+  </si>
+  <si>
+    <t>CK.gif</t>
+  </si>
+  <si>
+    <t>CL.gif</t>
+  </si>
+  <si>
+    <t>CM.gif</t>
+  </si>
+  <si>
+    <t>CN.gif</t>
+  </si>
+  <si>
+    <t>CO.gif</t>
+  </si>
+  <si>
+    <t>CR.gif</t>
+  </si>
+  <si>
+    <t>CU.gif</t>
+  </si>
+  <si>
+    <t>CV.gif</t>
+  </si>
+  <si>
+    <t>CY.gif</t>
+  </si>
+  <si>
+    <t>CZ.gif</t>
+  </si>
+  <si>
+    <t>DE.gif</t>
+  </si>
+  <si>
+    <t>DJ.gif</t>
+  </si>
+  <si>
+    <t>DK.gif</t>
+  </si>
+  <si>
+    <t>DM.gif</t>
+  </si>
+  <si>
+    <t>DO.bmp</t>
+  </si>
+  <si>
+    <t>DZ.gif</t>
+  </si>
+  <si>
+    <t>EC.gif</t>
+  </si>
+  <si>
+    <t>EE.gif</t>
+  </si>
+  <si>
+    <t>EG.gif</t>
+  </si>
+  <si>
+    <t>ER.gif</t>
+  </si>
+  <si>
+    <t>ES.gif</t>
+  </si>
+  <si>
+    <t>ET.gif</t>
+  </si>
+  <si>
+    <t>FI.gif</t>
+  </si>
+  <si>
+    <t>FJ.gif</t>
+  </si>
+  <si>
+    <t>FM.gif</t>
+  </si>
+  <si>
+    <t>FR.gif</t>
+  </si>
+  <si>
+    <t>GA.gif</t>
+  </si>
+  <si>
+    <t>GB.gif</t>
+  </si>
+  <si>
+    <t>GD.gif</t>
+  </si>
+  <si>
+    <t>GE.gif</t>
+  </si>
+  <si>
+    <t>GH.gif</t>
+  </si>
+  <si>
+    <t>GM.gif</t>
+  </si>
+  <si>
+    <t>GN.gif</t>
+  </si>
+  <si>
+    <t>GQ.gif</t>
+  </si>
+  <si>
+    <t>GR.gif</t>
+  </si>
+  <si>
+    <t>GT.gif</t>
+  </si>
+  <si>
+    <t>GW.gif</t>
+  </si>
+  <si>
+    <t>GY.gif</t>
+  </si>
+  <si>
+    <t>HN.gif</t>
+  </si>
+  <si>
+    <t>HR.gif</t>
+  </si>
+  <si>
+    <t>HT.gif</t>
+  </si>
+  <si>
+    <t>HU.gif</t>
+  </si>
+  <si>
+    <t>ID.gif</t>
+  </si>
+  <si>
+    <t>IE.gif</t>
+  </si>
+  <si>
+    <t>IL.gif</t>
+  </si>
+  <si>
+    <t>IN.gif</t>
+  </si>
+  <si>
+    <t>IQ.gif</t>
+  </si>
+  <si>
+    <t>IR.gif</t>
+  </si>
+  <si>
+    <t>IS.gif</t>
+  </si>
+  <si>
+    <t>IT.gif</t>
+  </si>
+  <si>
+    <t>JM.gif</t>
+  </si>
+  <si>
+    <t>JO.gif</t>
+  </si>
+  <si>
+    <t>JP.gif</t>
+  </si>
+  <si>
+    <t>KE.png</t>
+  </si>
+  <si>
+    <t>KG.gif</t>
+  </si>
+  <si>
+    <t>KH.jpg</t>
+  </si>
+  <si>
+    <t>KI.gif</t>
+  </si>
+  <si>
+    <t>KM.gif</t>
+  </si>
+  <si>
+    <t>KN.gif</t>
+  </si>
+  <si>
+    <t>KW.gif</t>
+  </si>
+  <si>
+    <t>KZ.gif</t>
+  </si>
+  <si>
+    <t>LA.gif</t>
+  </si>
+  <si>
+    <t>LB.gif</t>
+  </si>
+  <si>
+    <t>LC.bmp</t>
+  </si>
+  <si>
+    <t>LI.gif</t>
+  </si>
+  <si>
+    <t>LK.gif</t>
+  </si>
+  <si>
+    <t>LR.gif</t>
+  </si>
+  <si>
+    <t>LS.gif</t>
+  </si>
+  <si>
+    <t>LT.gif</t>
+  </si>
+  <si>
+    <t>LU.gif</t>
+  </si>
+  <si>
+    <t>LV.gif</t>
+  </si>
+  <si>
+    <t>LY.gif</t>
+  </si>
+  <si>
+    <t>MA.gif</t>
+  </si>
+  <si>
+    <t>MC.gif</t>
+  </si>
+  <si>
+    <t>MD.gif</t>
+  </si>
+  <si>
+    <t>ME.gif</t>
+  </si>
+  <si>
+    <t>MG.gif</t>
+  </si>
+  <si>
+    <t>MH.gif</t>
+  </si>
+  <si>
+    <t>MK.gif</t>
+  </si>
+  <si>
+    <t>ML.gif</t>
+  </si>
+  <si>
+    <t>MM.gif</t>
+  </si>
+  <si>
+    <t>MN.gif</t>
+  </si>
+  <si>
+    <t>MR.gif</t>
+  </si>
+  <si>
+    <t>MT.gif</t>
+  </si>
+  <si>
+    <t>MU.gif</t>
+  </si>
+  <si>
+    <t>MV.gif</t>
+  </si>
+  <si>
+    <t>MW.gif</t>
+  </si>
+  <si>
+    <t>MX.gif</t>
+  </si>
+  <si>
+    <t>MY.gif</t>
+  </si>
+  <si>
+    <t>MZ.gif</t>
+  </si>
+  <si>
+    <t>NA.gif</t>
+  </si>
+  <si>
+    <t>NE.gif</t>
+  </si>
+  <si>
+    <t>NG.gif</t>
+  </si>
+  <si>
+    <t>NI.gif</t>
+  </si>
+  <si>
+    <t>NL.gif</t>
+  </si>
+  <si>
+    <t>NO.gif</t>
+  </si>
+  <si>
+    <t>NP.gif</t>
+  </si>
+  <si>
+    <t>NR.gif</t>
+  </si>
+  <si>
+    <t>NU.png</t>
+  </si>
+  <si>
+    <t>NZ.gif</t>
+  </si>
+  <si>
+    <t>OM.gif</t>
+  </si>
+  <si>
+    <t>PA.gif</t>
+  </si>
+  <si>
+    <t>PE.gif</t>
+  </si>
+  <si>
+    <t>PG.gif</t>
+  </si>
+  <si>
+    <t>PH.gif</t>
+  </si>
+  <si>
+    <t>PK.gif</t>
+  </si>
+  <si>
+    <t>PL.png</t>
+  </si>
+  <si>
+    <t>PS.gif</t>
+  </si>
+  <si>
+    <t>PT.gif</t>
+  </si>
+  <si>
+    <t>PW.gif</t>
+  </si>
+  <si>
+    <t>PY.gif</t>
+  </si>
+  <si>
+    <t>QA.gif</t>
+  </si>
+  <si>
+    <t>RO.gif</t>
+  </si>
+  <si>
+    <t>RS.gif</t>
+  </si>
+  <si>
+    <t>RU.gif</t>
+  </si>
+  <si>
+    <t>RW.gif</t>
+  </si>
+  <si>
+    <t>SA.gif</t>
+  </si>
+  <si>
+    <t>SB.gif</t>
+  </si>
+  <si>
+    <t>SC.gif</t>
+  </si>
+  <si>
+    <t>SD.gif</t>
+  </si>
+  <si>
+    <t>SE.gif</t>
+  </si>
+  <si>
+    <t>SG.gif</t>
+  </si>
+  <si>
+    <t>SI.gif</t>
+  </si>
+  <si>
+    <t>SK.gif</t>
+  </si>
+  <si>
+    <t>SL.gif</t>
+  </si>
+  <si>
+    <t>SM.gif</t>
+  </si>
+  <si>
+    <t>SN.gif</t>
+  </si>
+  <si>
+    <t>SO.gif</t>
+  </si>
+  <si>
+    <t>SR.gif</t>
+  </si>
+  <si>
+    <t>SS.gif</t>
+  </si>
+  <si>
+    <t>ST.gif</t>
+  </si>
+  <si>
+    <t>SV.bmp</t>
+  </si>
+  <si>
+    <t>SY.gif</t>
+  </si>
+  <si>
+    <t>SZ.gif</t>
+  </si>
+  <si>
+    <t>TD.gif</t>
+  </si>
+  <si>
+    <t>TG.gif</t>
+  </si>
+  <si>
+    <t>TH.gif</t>
+  </si>
+  <si>
+    <t>TJ.gif</t>
+  </si>
+  <si>
+    <t>TL.gif</t>
+  </si>
+  <si>
+    <t>TM.gif</t>
+  </si>
+  <si>
+    <t>TN.gif</t>
+  </si>
+  <si>
+    <t>TO.gif</t>
+  </si>
+  <si>
+    <t>TR.gif</t>
+  </si>
+  <si>
+    <t>TT.gif</t>
+  </si>
+  <si>
+    <t>TV.gif</t>
+  </si>
+  <si>
+    <t>TZ.gif</t>
+  </si>
+  <si>
+    <t>UA.gif</t>
+  </si>
+  <si>
+    <t>UG.gif</t>
+  </si>
+  <si>
+    <t>US.gif</t>
+  </si>
+  <si>
+    <t>UY.gif</t>
+  </si>
+  <si>
+    <t>UZ.gif</t>
+  </si>
+  <si>
+    <t>VA.gif</t>
+  </si>
+  <si>
+    <t>VC.gif</t>
+  </si>
+  <si>
+    <t>VE.gif</t>
+  </si>
+  <si>
+    <t>VN.gif</t>
+  </si>
+  <si>
+    <t>VU.gif</t>
+  </si>
+  <si>
+    <t>WS.gif</t>
+  </si>
+  <si>
+    <t>XK.gif</t>
+  </si>
+  <si>
+    <t>YE.gif</t>
+  </si>
+  <si>
+    <t>ZA.gif</t>
+  </si>
+  <si>
+    <t>ZM.gif</t>
+  </si>
+  <si>
+    <t>ZW.gif</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C298"/>
+  <dimension ref="A1:C265"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.3">
@@ -2545,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
@@ -2553,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
@@ -2561,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
@@ -2569,7 +2959,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
@@ -2577,7 +2967,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
@@ -2585,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
@@ -2593,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
@@ -2601,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
@@ -2609,7 +2999,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>306</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
@@ -2617,7 +3007,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
@@ -2625,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
@@ -2633,7 +3023,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
@@ -2641,7 +3031,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
@@ -2649,7 +3039,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
@@ -2657,7 +3047,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
@@ -2665,7 +3055,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -2673,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -2681,7 +3071,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -2689,7 +3079,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
@@ -2697,7 +3087,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -2705,7 +3095,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -2713,7 +3103,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>319</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
@@ -2721,7 +3111,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
@@ -2729,7 +3119,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
@@ -2737,7 +3127,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -2745,7 +3135,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -2753,7 +3143,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -2761,7 +3151,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -2769,7 +3159,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>523</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -2777,7 +3167,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -2785,7 +3175,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -2793,7 +3183,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -2801,7 +3191,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -2809,7 +3199,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -2817,7 +3207,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -2825,7 +3215,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -2833,7 +3223,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -2841,7 +3231,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -2849,7 +3239,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -2857,7 +3247,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -2865,7 +3255,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -2873,7 +3263,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
@@ -2881,7 +3271,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
@@ -2889,7 +3279,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -2897,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
@@ -2905,7 +3295,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -2913,7 +3303,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
@@ -2921,7 +3311,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
@@ -2929,7 +3319,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -2937,7 +3327,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
@@ -2945,7 +3335,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
@@ -2953,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
@@ -2961,7 +3351,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
@@ -2969,7 +3359,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -2977,7 +3367,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -2985,7 +3375,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -2993,7 +3383,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
@@ -3001,7 +3391,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -3009,7 +3399,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
@@ -3017,7 +3407,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
@@ -3025,7 +3415,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
@@ -3033,7 +3423,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3041,7 +3431,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
@@ -3049,7 +3439,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -3057,7 +3447,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -3065,7 +3455,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
@@ -3073,7 +3463,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
@@ -3081,7 +3471,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
@@ -3089,7 +3479,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
@@ -3097,7 +3487,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
@@ -3105,7 +3495,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
@@ -3113,7 +3503,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
@@ -3121,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
@@ -3129,7 +3519,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>370</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
@@ -3137,7 +3527,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>371</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
@@ -3145,7 +3535,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
@@ -3153,7 +3543,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
@@ -3161,7 +3551,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
@@ -3169,7 +3559,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
@@ -3177,7 +3567,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
@@ -3185,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
@@ -3193,7 +3583,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
@@ -3201,7 +3591,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
@@ -3209,7 +3599,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
@@ -3217,7 +3607,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
@@ -3225,7 +3615,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
@@ -3233,7 +3623,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>383</v>
+        <v>456</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
@@ -3241,7 +3631,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
@@ -3249,7 +3639,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
@@ -3257,7 +3647,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
@@ -3265,7 +3655,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
@@ -3273,7 +3663,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
@@ -3281,7 +3671,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
@@ -3289,7 +3679,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
@@ -3297,7 +3687,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
@@ -3305,7 +3695,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
@@ -3313,7 +3703,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
@@ -3321,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
@@ -3329,7 +3719,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
@@ -3337,7 +3727,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
@@ -3345,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
@@ -3353,7 +3743,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
@@ -3361,7 +3751,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>522</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
@@ -3369,7 +3759,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
@@ -3377,7 +3767,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
@@ -3385,7 +3775,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
@@ -3393,7 +3783,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>402</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
@@ -3401,7 +3791,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
@@ -3409,7 +3799,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
@@ -3417,7 +3807,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
@@ -3425,7 +3815,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
@@ -3433,7 +3823,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
@@ -3441,7 +3831,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
@@ -3449,7 +3839,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
@@ -3457,7 +3847,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
@@ -3465,7 +3855,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
@@ -3473,7 +3863,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
@@ -3481,7 +3871,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
@@ -3489,7 +3879,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
@@ -3497,7 +3887,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
@@ -3505,7 +3895,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
@@ -3513,7 +3903,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
@@ -3521,7 +3911,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
@@ -3529,7 +3919,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
@@ -3537,7 +3927,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
@@ -3545,7 +3935,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
@@ -3553,7 +3943,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
@@ -3561,7 +3951,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
@@ -3569,7 +3959,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.3">
@@ -3577,7 +3967,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
@@ -3585,7 +3975,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
@@ -3593,7 +3983,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.3">
@@ -3601,7 +3991,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.3">
@@ -3609,7 +3999,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.3">
@@ -3617,7 +4007,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
@@ -3625,7 +4015,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
@@ -3633,7 +4023,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.3">
@@ -3641,7 +4031,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.3">
@@ -3649,7 +4039,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
@@ -3657,7 +4047,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>521</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
@@ -3665,7 +4055,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.3">
@@ -3673,7 +4063,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.3">
@@ -3681,7 +4071,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.3">
@@ -3689,7 +4079,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.3">
@@ -3697,7 +4087,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.3">
@@ -3705,7 +4095,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.3">
@@ -3713,7 +4103,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
@@ -3721,7 +4111,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.3">
@@ -3729,7 +4119,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.3">
@@ -3737,7 +4127,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
@@ -3745,7 +4135,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
@@ -3753,7 +4143,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>446</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
@@ -3761,7 +4151,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
@@ -3769,7 +4159,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
@@ -3777,7 +4167,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.3">
@@ -3785,7 +4175,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.3">
@@ -3793,7 +4183,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.3">
@@ -3801,7 +4191,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.3">
@@ -3809,7 +4199,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>453</v>
+        <v>419</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.3">
@@ -3817,7 +4207,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
@@ -3825,7 +4215,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>455</v>
+        <v>421</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
@@ -3833,7 +4223,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.3">
@@ -3841,7 +4231,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
@@ -3849,7 +4239,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
@@ -3857,7 +4247,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>459</v>
+        <v>425</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.3">
@@ -3865,7 +4255,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.3">
@@ -3873,7 +4263,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.3">
@@ -3881,7 +4271,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.3">
@@ -3889,7 +4279,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.3">
@@ -3897,7 +4287,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.3">
@@ -3905,7 +4295,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.3">
@@ -3913,7 +4303,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
@@ -3921,7 +4311,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
@@ -3929,7 +4319,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.3">
@@ -3937,7 +4327,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>469</v>
+        <v>435</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
@@ -3945,7 +4335,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>470</v>
+        <v>436</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
@@ -3953,7 +4343,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
@@ -3961,7 +4351,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.3">
@@ -3969,7 +4359,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.3">
@@ -3977,7 +4367,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>520</v>
+        <v>440</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.3">
@@ -3985,7 +4375,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.3">
@@ -3993,7 +4383,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.3">
@@ -4001,7 +4391,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.3">
@@ -4009,7 +4399,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.3">
@@ -4017,7 +4407,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.3">
@@ -4025,7 +4415,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.3">
@@ -4033,7 +4423,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
@@ -4041,7 +4431,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
@@ -4049,7 +4439,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.3">
@@ -4057,7 +4447,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
@@ -4065,7 +4455,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.3">
@@ -4073,295 +4463,324 @@
         <v>191</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B193" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B195" s="2" t="s">
+      <c r="B194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B196" s="2" t="s">
+      <c r="B195">
+        <v>4</v>
+      </c>
+      <c r="C195" s="2"/>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B197" s="2" t="s">
+      <c r="B196">
+        <v>6</v>
+      </c>
+      <c r="C196" s="2"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B198" s="2" t="s">
+      <c r="B197" s="2">
+        <v>8</v>
+      </c>
+      <c r="C197" s="2"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B199" s="2" t="s">
+      <c r="B198" s="2">
+        <v>10</v>
+      </c>
+      <c r="C198" s="2"/>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B200" s="2" t="s">
+      <c r="B199" s="2">
+        <v>12</v>
+      </c>
+      <c r="C199" s="2"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B201" s="2" t="s">
+      <c r="B200" s="2">
+        <v>14</v>
+      </c>
+      <c r="C200" s="2"/>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B202" s="2" t="s">
+      <c r="B201" s="2">
+        <v>16</v>
+      </c>
+      <c r="C201" s="2"/>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B203" s="2" t="s">
+      <c r="B202" s="2">
+        <v>18</v>
+      </c>
+      <c r="C202" s="2"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B204" s="2" t="s">
+      <c r="B203">
+        <v>3</v>
+      </c>
+      <c r="C203" s="2"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B205" s="2" t="s">
+      <c r="B204">
+        <v>6</v>
+      </c>
+      <c r="C204" s="2"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B206" s="2" t="s">
+      <c r="B205">
+        <v>9</v>
+      </c>
+      <c r="C205" s="2"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B207" s="2" t="s">
+      <c r="B206" s="2">
+        <v>12</v>
+      </c>
+      <c r="C206" s="2"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B208" s="2" t="s">
+      <c r="B207" s="2">
+        <v>15</v>
+      </c>
+      <c r="C207" s="2"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B209" s="2" t="s">
+      <c r="B208" s="2">
+        <v>18</v>
+      </c>
+      <c r="C208" s="2"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B210" s="2" t="s">
+      <c r="B209" s="2">
+        <v>21</v>
+      </c>
+      <c r="C209" s="2"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B211" s="2" t="s">
+      <c r="B210" s="2">
+        <v>24</v>
+      </c>
+      <c r="C210" s="2"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B212" s="2" t="s">
+      <c r="B211" s="2">
+        <v>27</v>
+      </c>
+      <c r="C211" s="2"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B213" s="2" t="s">
+      <c r="B212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B214" s="2" t="s">
+      <c r="B213">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B215" s="2" t="s">
+      <c r="B214">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B216" s="2" t="s">
+      <c r="B215">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B217" s="2" t="s">
+      <c r="B216" s="2">
+        <v>20</v>
+      </c>
+      <c r="C216" s="2"/>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="1" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B218" s="2" t="s">
+      <c r="B217" s="2">
+        <v>24</v>
+      </c>
+      <c r="C217" s="2"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B219" s="2" t="s">
+      <c r="B218" s="2">
+        <v>28</v>
+      </c>
+      <c r="C218" s="2"/>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B220" s="2" t="s">
+      <c r="B219" s="2">
+        <v>32</v>
+      </c>
+      <c r="C219" s="2"/>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B221" s="2" t="s">
+      <c r="B220" s="2">
+        <v>36</v>
+      </c>
+      <c r="C220" s="2"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B222" s="2" t="s">
+      <c r="B221">
+        <v>5</v>
+      </c>
+      <c r="C221" s="2"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B223" s="2" t="s">
+      <c r="B222">
+        <v>10</v>
+      </c>
+      <c r="C222" s="2"/>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B224" s="2" t="s">
+      <c r="B223">
+        <v>15</v>
+      </c>
+      <c r="C223" s="2"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>517</v>
-      </c>
+      <c r="B224">
+        <v>20</v>
+      </c>
+      <c r="C224" s="2"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B225" s="2" t="s">
+      <c r="A225" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>518</v>
-      </c>
+      <c r="B225">
+        <v>25</v>
+      </c>
+      <c r="C225" s="2"/>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B226" s="2" t="s">
+      <c r="A226" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>519</v>
-      </c>
+      <c r="B226" s="2">
+        <v>30</v>
+      </c>
+      <c r="C226" s="2"/>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>226</v>
       </c>
-      <c r="B227">
-        <v>2</v>
-      </c>
+      <c r="B227" s="2">
+        <v>35</v>
+      </c>
+      <c r="C227" s="2"/>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>227</v>
       </c>
-      <c r="B228">
-        <v>4</v>
+      <c r="B228" s="2">
+        <v>40</v>
       </c>
       <c r="C228" s="2"/>
     </row>
@@ -4369,8 +4788,8 @@
       <c r="A229" t="s">
         <v>228</v>
       </c>
-      <c r="B229">
-        <v>6</v>
+      <c r="B229" s="2">
+        <v>45</v>
       </c>
       <c r="C229" s="2"/>
     </row>
@@ -4378,8 +4797,8 @@
       <c r="A230" t="s">
         <v>229</v>
       </c>
-      <c r="B230" s="2">
-        <v>8</v>
+      <c r="B230">
+        <v>6</v>
       </c>
       <c r="C230" s="2"/>
     </row>
@@ -4387,8 +4806,8 @@
       <c r="A231" t="s">
         <v>230</v>
       </c>
-      <c r="B231" s="2">
-        <v>10</v>
+      <c r="B231">
+        <v>12</v>
       </c>
       <c r="C231" s="2"/>
     </row>
@@ -4396,8 +4815,8 @@
       <c r="A232" t="s">
         <v>231</v>
       </c>
-      <c r="B232" s="2">
-        <v>12</v>
+      <c r="B232">
+        <v>18</v>
       </c>
       <c r="C232" s="2"/>
     </row>
@@ -4405,8 +4824,8 @@
       <c r="A233" t="s">
         <v>232</v>
       </c>
-      <c r="B233" s="2">
-        <v>14</v>
+      <c r="B233">
+        <v>24</v>
       </c>
       <c r="C233" s="2"/>
     </row>
@@ -4414,8 +4833,8 @@
       <c r="A234" t="s">
         <v>233</v>
       </c>
-      <c r="B234" s="2">
-        <v>16</v>
+      <c r="B234">
+        <v>30</v>
       </c>
       <c r="C234" s="2"/>
     </row>
@@ -4424,7 +4843,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C235" s="2"/>
     </row>
@@ -4432,8 +4851,8 @@
       <c r="A236" t="s">
         <v>235</v>
       </c>
-      <c r="B236">
-        <v>3</v>
+      <c r="B236" s="2">
+        <v>42</v>
       </c>
       <c r="C236" s="2"/>
     </row>
@@ -4441,8 +4860,8 @@
       <c r="A237" t="s">
         <v>236</v>
       </c>
-      <c r="B237">
-        <v>6</v>
+      <c r="B237" s="2">
+        <v>48</v>
       </c>
       <c r="C237" s="2"/>
     </row>
@@ -4450,8 +4869,8 @@
       <c r="A238" t="s">
         <v>237</v>
       </c>
-      <c r="B238">
-        <v>9</v>
+      <c r="B238" s="2">
+        <v>54</v>
       </c>
       <c r="C238" s="2"/>
     </row>
@@ -4459,8 +4878,8 @@
       <c r="A239" t="s">
         <v>238</v>
       </c>
-      <c r="B239" s="2">
-        <v>12</v>
+      <c r="B239">
+        <v>7</v>
       </c>
       <c r="C239" s="2"/>
     </row>
@@ -4468,8 +4887,8 @@
       <c r="A240" t="s">
         <v>239</v>
       </c>
-      <c r="B240" s="2">
-        <v>15</v>
+      <c r="B240">
+        <v>14</v>
       </c>
       <c r="C240" s="2"/>
     </row>
@@ -4477,8 +4896,8 @@
       <c r="A241" t="s">
         <v>240</v>
       </c>
-      <c r="B241" s="2">
-        <v>18</v>
+      <c r="B241">
+        <v>21</v>
       </c>
       <c r="C241" s="2"/>
     </row>
@@ -4486,8 +4905,8 @@
       <c r="A242" t="s">
         <v>241</v>
       </c>
-      <c r="B242" s="2">
-        <v>21</v>
+      <c r="B242">
+        <v>28</v>
       </c>
       <c r="C242" s="2"/>
     </row>
@@ -4495,8 +4914,8 @@
       <c r="A243" t="s">
         <v>242</v>
       </c>
-      <c r="B243" s="2">
-        <v>24</v>
+      <c r="B243">
+        <v>35</v>
       </c>
       <c r="C243" s="2"/>
     </row>
@@ -4505,7 +4924,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C244" s="2"/>
     </row>
@@ -4513,40 +4932,44 @@
       <c r="A245" t="s">
         <v>244</v>
       </c>
-      <c r="B245">
-        <v>4</v>
-      </c>
+      <c r="B245" s="2">
+        <v>49</v>
+      </c>
+      <c r="C245" s="2"/>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>245</v>
       </c>
-      <c r="B246">
-        <v>8</v>
-      </c>
+      <c r="B246" s="2">
+        <v>56</v>
+      </c>
+      <c r="C246" s="2"/>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>246</v>
       </c>
-      <c r="B247">
-        <v>12</v>
-      </c>
+      <c r="B247" s="2">
+        <v>63</v>
+      </c>
+      <c r="C247" s="2"/>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>247</v>
       </c>
       <c r="B248">
-        <v>16</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C248" s="2"/>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>248</v>
       </c>
-      <c r="B249" s="2">
-        <v>20</v>
+      <c r="B249">
+        <v>16</v>
       </c>
       <c r="C249" s="2"/>
     </row>
@@ -4554,7 +4977,7 @@
       <c r="A250" t="s">
         <v>249</v>
       </c>
-      <c r="B250" s="2">
+      <c r="B250">
         <v>24</v>
       </c>
       <c r="C250" s="2"/>
@@ -4564,7 +4987,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C251" s="2"/>
     </row>
@@ -4573,7 +4996,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C252" s="2"/>
     </row>
@@ -4582,7 +5005,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C253" s="2"/>
     </row>
@@ -4590,8 +5013,8 @@
       <c r="A254" t="s">
         <v>253</v>
       </c>
-      <c r="B254">
-        <v>5</v>
+      <c r="B254" s="2">
+        <v>56</v>
       </c>
       <c r="C254" s="2"/>
     </row>
@@ -4599,8 +5022,8 @@
       <c r="A255" t="s">
         <v>254</v>
       </c>
-      <c r="B255">
-        <v>10</v>
+      <c r="B255" s="2">
+        <v>64</v>
       </c>
       <c r="C255" s="2"/>
     </row>
@@ -4608,8 +5031,8 @@
       <c r="A256" t="s">
         <v>255</v>
       </c>
-      <c r="B256">
-        <v>15</v>
+      <c r="B256" s="2">
+        <v>72</v>
       </c>
       <c r="C256" s="2"/>
     </row>
@@ -4618,7 +5041,7 @@
         <v>256</v>
       </c>
       <c r="B257">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C257" s="2"/>
     </row>
@@ -4627,7 +5050,7 @@
         <v>257</v>
       </c>
       <c r="B258">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C258" s="2"/>
     </row>
@@ -4635,8 +5058,8 @@
       <c r="A259" t="s">
         <v>258</v>
       </c>
-      <c r="B259" s="2">
-        <v>30</v>
+      <c r="B259">
+        <v>27</v>
       </c>
       <c r="C259" s="2"/>
     </row>
@@ -4645,7 +5068,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C260" s="2"/>
     </row>
@@ -4654,7 +5077,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C261" s="2"/>
     </row>
@@ -4663,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C262" s="2"/>
     </row>
@@ -4671,8 +5094,8 @@
       <c r="A263" t="s">
         <v>262</v>
       </c>
-      <c r="B263">
-        <v>6</v>
+      <c r="B263" s="2">
+        <v>63</v>
       </c>
       <c r="C263" s="2"/>
     </row>
@@ -4680,8 +5103,8 @@
       <c r="A264" t="s">
         <v>263</v>
       </c>
-      <c r="B264">
-        <v>12</v>
+      <c r="B264" s="2">
+        <v>72</v>
       </c>
       <c r="C264" s="2"/>
     </row>
@@ -4689,307 +5112,10 @@
       <c r="A265" t="s">
         <v>264</v>
       </c>
-      <c r="B265">
-        <v>18</v>
+      <c r="B265" s="2">
+        <v>81</v>
       </c>
       <c r="C265" s="2"/>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>265</v>
-      </c>
-      <c r="B266">
-        <v>24</v>
-      </c>
-      <c r="C266" s="2"/>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>266</v>
-      </c>
-      <c r="B267">
-        <v>30</v>
-      </c>
-      <c r="C267" s="2"/>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>267</v>
-      </c>
-      <c r="B268" s="2">
-        <v>36</v>
-      </c>
-      <c r="C268" s="2"/>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>268</v>
-      </c>
-      <c r="B269" s="2">
-        <v>42</v>
-      </c>
-      <c r="C269" s="2"/>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>269</v>
-      </c>
-      <c r="B270" s="2">
-        <v>48</v>
-      </c>
-      <c r="C270" s="2"/>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>270</v>
-      </c>
-      <c r="B271" s="2">
-        <v>54</v>
-      </c>
-      <c r="C271" s="2"/>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>271</v>
-      </c>
-      <c r="B272">
-        <v>7</v>
-      </c>
-      <c r="C272" s="2"/>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>272</v>
-      </c>
-      <c r="B273">
-        <v>14</v>
-      </c>
-      <c r="C273" s="2"/>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>273</v>
-      </c>
-      <c r="B274">
-        <v>21</v>
-      </c>
-      <c r="C274" s="2"/>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>274</v>
-      </c>
-      <c r="B275">
-        <v>28</v>
-      </c>
-      <c r="C275" s="2"/>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>275</v>
-      </c>
-      <c r="B276">
-        <v>35</v>
-      </c>
-      <c r="C276" s="2"/>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>276</v>
-      </c>
-      <c r="B277" s="2">
-        <v>42</v>
-      </c>
-      <c r="C277" s="2"/>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>277</v>
-      </c>
-      <c r="B278" s="2">
-        <v>49</v>
-      </c>
-      <c r="C278" s="2"/>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>278</v>
-      </c>
-      <c r="B279" s="2">
-        <v>56</v>
-      </c>
-      <c r="C279" s="2"/>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>279</v>
-      </c>
-      <c r="B280" s="2">
-        <v>63</v>
-      </c>
-      <c r="C280" s="2"/>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>280</v>
-      </c>
-      <c r="B281">
-        <v>8</v>
-      </c>
-      <c r="C281" s="2"/>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>281</v>
-      </c>
-      <c r="B282">
-        <v>16</v>
-      </c>
-      <c r="C282" s="2"/>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>282</v>
-      </c>
-      <c r="B283">
-        <v>24</v>
-      </c>
-      <c r="C283" s="2"/>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>283</v>
-      </c>
-      <c r="B284" s="2">
-        <v>32</v>
-      </c>
-      <c r="C284" s="2"/>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>284</v>
-      </c>
-      <c r="B285" s="2">
-        <v>40</v>
-      </c>
-      <c r="C285" s="2"/>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>285</v>
-      </c>
-      <c r="B286" s="2">
-        <v>48</v>
-      </c>
-      <c r="C286" s="2"/>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>286</v>
-      </c>
-      <c r="B287" s="2">
-        <v>56</v>
-      </c>
-      <c r="C287" s="2"/>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>287</v>
-      </c>
-      <c r="B288" s="2">
-        <v>64</v>
-      </c>
-      <c r="C288" s="2"/>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>288</v>
-      </c>
-      <c r="B289" s="2">
-        <v>72</v>
-      </c>
-      <c r="C289" s="2"/>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>289</v>
-      </c>
-      <c r="B290">
-        <v>9</v>
-      </c>
-      <c r="C290" s="2"/>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>290</v>
-      </c>
-      <c r="B291">
-        <v>18</v>
-      </c>
-      <c r="C291" s="2"/>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>291</v>
-      </c>
-      <c r="B292">
-        <v>27</v>
-      </c>
-      <c r="C292" s="2"/>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>292</v>
-      </c>
-      <c r="B293" s="2">
-        <v>36</v>
-      </c>
-      <c r="C293" s="2"/>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>293</v>
-      </c>
-      <c r="B294" s="2">
-        <v>45</v>
-      </c>
-      <c r="C294" s="2"/>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>294</v>
-      </c>
-      <c r="B295" s="2">
-        <v>54</v>
-      </c>
-      <c r="C295" s="2"/>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>295</v>
-      </c>
-      <c r="B296" s="2">
-        <v>63</v>
-      </c>
-      <c r="C296" s="2"/>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>296</v>
-      </c>
-      <c r="B297" s="2">
-        <v>72</v>
-      </c>
-      <c r="C297" s="2"/>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>297</v>
-      </c>
-      <c r="B298" s="2">
-        <v>81</v>
-      </c>
-      <c r="C298" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -5000,9 +5126,990 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A196"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>653</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/flash.xlsx
+++ b/flash.xlsx
@@ -597,222 +597,6 @@
     <t>호주</t>
   </si>
   <si>
-    <t>2x1</t>
-  </si>
-  <si>
-    <t>2x2</t>
-  </si>
-  <si>
-    <t>2x3</t>
-  </si>
-  <si>
-    <t>2x4</t>
-  </si>
-  <si>
-    <t>2x5</t>
-  </si>
-  <si>
-    <t>2x6</t>
-  </si>
-  <si>
-    <t>2x7</t>
-  </si>
-  <si>
-    <t>2x8</t>
-  </si>
-  <si>
-    <t>2x9</t>
-  </si>
-  <si>
-    <t>3x1</t>
-  </si>
-  <si>
-    <t>3x2</t>
-  </si>
-  <si>
-    <t>3x3</t>
-  </si>
-  <si>
-    <t>3x4</t>
-  </si>
-  <si>
-    <t>3x5</t>
-  </si>
-  <si>
-    <t>3x6</t>
-  </si>
-  <si>
-    <t>3x7</t>
-  </si>
-  <si>
-    <t>3x8</t>
-  </si>
-  <si>
-    <t>3x9</t>
-  </si>
-  <si>
-    <t>4x1</t>
-  </si>
-  <si>
-    <t>4x2</t>
-  </si>
-  <si>
-    <t>4x3</t>
-  </si>
-  <si>
-    <t>4x4</t>
-  </si>
-  <si>
-    <t>4x5</t>
-  </si>
-  <si>
-    <t>4x6</t>
-  </si>
-  <si>
-    <t>4x7</t>
-  </si>
-  <si>
-    <t>4x8</t>
-  </si>
-  <si>
-    <t>4x9</t>
-  </si>
-  <si>
-    <t>5x1</t>
-  </si>
-  <si>
-    <t>5x2</t>
-  </si>
-  <si>
-    <t>5x3</t>
-  </si>
-  <si>
-    <t>5x4</t>
-  </si>
-  <si>
-    <t>5x5</t>
-  </si>
-  <si>
-    <t>5x6</t>
-  </si>
-  <si>
-    <t>5x7</t>
-  </si>
-  <si>
-    <t>5x8</t>
-  </si>
-  <si>
-    <t>5x9</t>
-  </si>
-  <si>
-    <t>6x1</t>
-  </si>
-  <si>
-    <t>6x2</t>
-  </si>
-  <si>
-    <t>6x3</t>
-  </si>
-  <si>
-    <t>6x4</t>
-  </si>
-  <si>
-    <t>6x5</t>
-  </si>
-  <si>
-    <t>6x6</t>
-  </si>
-  <si>
-    <t>6x7</t>
-  </si>
-  <si>
-    <t>6x8</t>
-  </si>
-  <si>
-    <t>6x9</t>
-  </si>
-  <si>
-    <t>7x1</t>
-  </si>
-  <si>
-    <t>7x2</t>
-  </si>
-  <si>
-    <t>7x3</t>
-  </si>
-  <si>
-    <t>7x4</t>
-  </si>
-  <si>
-    <t>7x5</t>
-  </si>
-  <si>
-    <t>7x6</t>
-  </si>
-  <si>
-    <t>7x7</t>
-  </si>
-  <si>
-    <t>7x8</t>
-  </si>
-  <si>
-    <t>7x9</t>
-  </si>
-  <si>
-    <t>8x1</t>
-  </si>
-  <si>
-    <t>8x2</t>
-  </si>
-  <si>
-    <t>8x3</t>
-  </si>
-  <si>
-    <t>8x4</t>
-  </si>
-  <si>
-    <t>8x5</t>
-  </si>
-  <si>
-    <t>8x6</t>
-  </si>
-  <si>
-    <t>8x7</t>
-  </si>
-  <si>
-    <t>8x8</t>
-  </si>
-  <si>
-    <t>8x9</t>
-  </si>
-  <si>
-    <t>9x1</t>
-  </si>
-  <si>
-    <t>9x2</t>
-  </si>
-  <si>
-    <t>9x3</t>
-  </si>
-  <si>
-    <t>9x4</t>
-  </si>
-  <si>
-    <t>9x5</t>
-  </si>
-  <si>
-    <t>9x6</t>
-  </si>
-  <si>
-    <t>9x7</t>
-  </si>
-  <si>
-    <t>9x8</t>
-  </si>
-  <si>
-    <t>9x9</t>
-  </si>
-  <si>
     <t>images/GH.gif</t>
   </si>
   <si>
@@ -1982,6 +1766,222 @@
   </si>
   <si>
     <t>ZW.gif</t>
+  </si>
+  <si>
+    <t>2 x 1</t>
+  </si>
+  <si>
+    <t>2 x 2</t>
+  </si>
+  <si>
+    <t>2 x 3</t>
+  </si>
+  <si>
+    <t>2 x 4</t>
+  </si>
+  <si>
+    <t>2 x 5</t>
+  </si>
+  <si>
+    <t>2 x 6</t>
+  </si>
+  <si>
+    <t>2 x 7</t>
+  </si>
+  <si>
+    <t>2 x 8</t>
+  </si>
+  <si>
+    <t>2 x 9</t>
+  </si>
+  <si>
+    <t>3 x 1</t>
+  </si>
+  <si>
+    <t>3 x 2</t>
+  </si>
+  <si>
+    <t>3 x 3</t>
+  </si>
+  <si>
+    <t>3 x 4</t>
+  </si>
+  <si>
+    <t>3 x 5</t>
+  </si>
+  <si>
+    <t>3 x 6</t>
+  </si>
+  <si>
+    <t>3 x 7</t>
+  </si>
+  <si>
+    <t>3 x 8</t>
+  </si>
+  <si>
+    <t>3 x 9</t>
+  </si>
+  <si>
+    <t>4 x 1</t>
+  </si>
+  <si>
+    <t>4 x 2</t>
+  </si>
+  <si>
+    <t>4 x 3</t>
+  </si>
+  <si>
+    <t>4 x 4</t>
+  </si>
+  <si>
+    <t>4 x 5</t>
+  </si>
+  <si>
+    <t>4 x 6</t>
+  </si>
+  <si>
+    <t>4 x 7</t>
+  </si>
+  <si>
+    <t>4 x 8</t>
+  </si>
+  <si>
+    <t>4 x 9</t>
+  </si>
+  <si>
+    <t>5 x 1</t>
+  </si>
+  <si>
+    <t>5 x 2</t>
+  </si>
+  <si>
+    <t>5 x 3</t>
+  </si>
+  <si>
+    <t>5 x 4</t>
+  </si>
+  <si>
+    <t>5 x 5</t>
+  </si>
+  <si>
+    <t>5 x 6</t>
+  </si>
+  <si>
+    <t>5 x 7</t>
+  </si>
+  <si>
+    <t>5 x 8</t>
+  </si>
+  <si>
+    <t>5 x 9</t>
+  </si>
+  <si>
+    <t>6 x 1</t>
+  </si>
+  <si>
+    <t>6 x 2</t>
+  </si>
+  <si>
+    <t>6 x 3</t>
+  </si>
+  <si>
+    <t>6 x 4</t>
+  </si>
+  <si>
+    <t>6 x 5</t>
+  </si>
+  <si>
+    <t>6 x 6</t>
+  </si>
+  <si>
+    <t>6 x 7</t>
+  </si>
+  <si>
+    <t>6 x 8</t>
+  </si>
+  <si>
+    <t>6 x 9</t>
+  </si>
+  <si>
+    <t>7 x 1</t>
+  </si>
+  <si>
+    <t>7 x 2</t>
+  </si>
+  <si>
+    <t>7 x 3</t>
+  </si>
+  <si>
+    <t>7 x 4</t>
+  </si>
+  <si>
+    <t>7 x 5</t>
+  </si>
+  <si>
+    <t>7 x 6</t>
+  </si>
+  <si>
+    <t>7 x 7</t>
+  </si>
+  <si>
+    <t>7 x 8</t>
+  </si>
+  <si>
+    <t>7 x 9</t>
+  </si>
+  <si>
+    <t>8 x 1</t>
+  </si>
+  <si>
+    <t>8 x 2</t>
+  </si>
+  <si>
+    <t>8 x 3</t>
+  </si>
+  <si>
+    <t>8 x 4</t>
+  </si>
+  <si>
+    <t>8 x 5</t>
+  </si>
+  <si>
+    <t>8 x 6</t>
+  </si>
+  <si>
+    <t>8 x 7</t>
+  </si>
+  <si>
+    <t>8 x 8</t>
+  </si>
+  <si>
+    <t>8 x 9</t>
+  </si>
+  <si>
+    <t>9 x 1</t>
+  </si>
+  <si>
+    <t>9 x 2</t>
+  </si>
+  <si>
+    <t>9 x 3</t>
+  </si>
+  <si>
+    <t>9 x 4</t>
+  </si>
+  <si>
+    <t>9 x 5</t>
+  </si>
+  <si>
+    <t>9 x 6</t>
+  </si>
+  <si>
+    <t>9 x 7</t>
+  </si>
+  <si>
+    <t>9 x 8</t>
+  </si>
+  <si>
+    <t>9 x 9</t>
   </si>
 </sst>
 </file>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>266</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
@@ -2951,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
@@ -2959,7 +2959,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
@@ -2967,7 +2967,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
@@ -2975,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
@@ -2983,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
@@ -2991,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
@@ -2999,7 +2999,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
@@ -3007,7 +3007,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
@@ -3023,7 +3023,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
@@ -3031,7 +3031,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>277</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
@@ -3039,7 +3039,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
@@ -3047,7 +3047,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
@@ -3055,7 +3055,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -3063,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -3071,7 +3071,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>282</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -3079,7 +3079,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
@@ -3087,7 +3087,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -3095,7 +3095,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>285</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -3103,7 +3103,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
@@ -3111,7 +3111,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
@@ -3119,7 +3119,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
@@ -3127,7 +3127,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -3135,7 +3135,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -3143,7 +3143,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -3151,7 +3151,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -3159,7 +3159,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -3167,7 +3167,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -3175,7 +3175,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -3183,7 +3183,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -3191,7 +3191,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -3199,7 +3199,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -3207,7 +3207,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -3215,7 +3215,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>299</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -3223,7 +3223,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>300</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -3231,7 +3231,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>301</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -3239,7 +3239,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -3255,7 +3255,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -3263,7 +3263,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
@@ -3271,7 +3271,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>306</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
@@ -3279,7 +3279,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>307</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -3287,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
@@ -3295,7 +3295,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>309</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -3303,7 +3303,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
@@ -3311,7 +3311,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
@@ -3319,7 +3319,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -3327,7 +3327,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
@@ -3335,7 +3335,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>314</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
@@ -3343,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>315</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
@@ -3351,7 +3351,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
@@ -3359,7 +3359,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -3367,7 +3367,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -3375,7 +3375,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -3383,7 +3383,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
@@ -3391,7 +3391,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -3399,7 +3399,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
@@ -3407,7 +3407,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>323</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
@@ -3415,7 +3415,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>324</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
@@ -3423,7 +3423,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>325</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3431,7 +3431,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
@@ -3439,7 +3439,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>327</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -3447,7 +3447,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>328</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -3455,7 +3455,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>329</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
@@ -3463,7 +3463,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
@@ -3471,7 +3471,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>331</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
@@ -3479,7 +3479,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>332</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
@@ -3487,7 +3487,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
@@ -3495,7 +3495,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>334</v>
+        <v>262</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
@@ -3503,7 +3503,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>335</v>
+        <v>263</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
@@ -3511,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
@@ -3519,7 +3519,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
@@ -3527,7 +3527,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
@@ -3535,7 +3535,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
@@ -3543,7 +3543,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
@@ -3551,7 +3551,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>341</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
@@ -3559,7 +3559,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>342</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
@@ -3567,7 +3567,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>343</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
@@ -3575,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
@@ -3583,7 +3583,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>345</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
@@ -3591,7 +3591,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>346</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
@@ -3599,7 +3599,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>347</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
@@ -3607,7 +3607,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
@@ -3615,7 +3615,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>349</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
@@ -3623,7 +3623,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
@@ -3631,7 +3631,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>350</v>
+        <v>278</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
@@ -3639,7 +3639,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
@@ -3647,7 +3647,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>352</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
@@ -3655,7 +3655,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
@@ -3663,7 +3663,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>354</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
@@ -3671,7 +3671,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
@@ -3679,7 +3679,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>356</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
@@ -3687,7 +3687,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>357</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
@@ -3695,7 +3695,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>358</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
@@ -3703,7 +3703,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>359</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
@@ -3711,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>360</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
@@ -3719,7 +3719,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>361</v>
+        <v>289</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
@@ -3727,7 +3727,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>362</v>
+        <v>290</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
@@ -3735,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
@@ -3743,7 +3743,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
@@ -3751,7 +3751,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
@@ -3759,7 +3759,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>366</v>
+        <v>294</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
@@ -3767,7 +3767,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>367</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
@@ -3775,7 +3775,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>368</v>
+        <v>296</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
@@ -3783,7 +3783,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>369</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
@@ -3791,7 +3791,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>370</v>
+        <v>298</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
@@ -3799,7 +3799,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
@@ -3807,7 +3807,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
@@ -3815,7 +3815,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>373</v>
+        <v>301</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
@@ -3823,7 +3823,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>374</v>
+        <v>302</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
@@ -3831,7 +3831,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>375</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
@@ -3839,7 +3839,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>376</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
@@ -3847,7 +3847,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>377</v>
+        <v>305</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
@@ -3855,7 +3855,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>378</v>
+        <v>306</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
@@ -3863,7 +3863,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
@@ -3871,7 +3871,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>380</v>
+        <v>308</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
@@ -3879,7 +3879,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>381</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
@@ -3887,7 +3887,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
@@ -3895,7 +3895,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>455</v>
+        <v>383</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
@@ -3903,7 +3903,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
@@ -3911,7 +3911,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>384</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
@@ -3919,7 +3919,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>385</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
@@ -3927,7 +3927,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>386</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
@@ -3935,7 +3935,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>387</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
@@ -3943,7 +3943,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
@@ -3951,7 +3951,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>389</v>
+        <v>317</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
@@ -3959,7 +3959,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.3">
@@ -3967,7 +3967,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
@@ -3975,7 +3975,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
@@ -3983,7 +3983,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.3">
@@ -3991,7 +3991,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.3">
@@ -3999,7 +3999,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.3">
@@ -4007,7 +4007,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
@@ -4015,7 +4015,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>397</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
@@ -4023,7 +4023,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>398</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.3">
@@ -4031,7 +4031,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>399</v>
+        <v>327</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.3">
@@ -4039,7 +4039,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
@@ -4047,7 +4047,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
@@ -4055,7 +4055,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.3">
@@ -4063,7 +4063,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>403</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.3">
@@ -4071,7 +4071,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>404</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.3">
@@ -4079,7 +4079,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>405</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.3">
@@ -4087,7 +4087,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>406</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>407</v>
+        <v>335</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.3">
@@ -4103,7 +4103,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
@@ -4111,7 +4111,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>409</v>
+        <v>337</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.3">
@@ -4119,7 +4119,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.3">
@@ -4127,7 +4127,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
@@ -4135,7 +4135,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
@@ -4143,7 +4143,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>413</v>
+        <v>341</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
@@ -4151,7 +4151,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>414</v>
+        <v>342</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
@@ -4159,7 +4159,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>415</v>
+        <v>343</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
@@ -4167,7 +4167,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.3">
@@ -4175,7 +4175,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>416</v>
+        <v>344</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.3">
@@ -4183,7 +4183,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>417</v>
+        <v>345</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.3">
@@ -4191,7 +4191,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.3">
@@ -4199,7 +4199,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>419</v>
+        <v>347</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.3">
@@ -4207,7 +4207,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
@@ -4215,7 +4215,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>421</v>
+        <v>349</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
@@ -4223,7 +4223,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>422</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.3">
@@ -4231,7 +4231,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
@@ -4239,7 +4239,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>424</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
@@ -4247,7 +4247,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>425</v>
+        <v>353</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.3">
@@ -4255,7 +4255,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>426</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.3">
@@ -4263,7 +4263,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>427</v>
+        <v>355</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.3">
@@ -4271,7 +4271,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>428</v>
+        <v>356</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.3">
@@ -4279,7 +4279,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>429</v>
+        <v>357</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.3">
@@ -4287,7 +4287,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.3">
@@ -4295,7 +4295,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>431</v>
+        <v>359</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.3">
@@ -4303,7 +4303,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>432</v>
+        <v>360</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
@@ -4311,7 +4311,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>433</v>
+        <v>361</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
@@ -4319,7 +4319,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>434</v>
+        <v>362</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.3">
@@ -4327,7 +4327,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>435</v>
+        <v>363</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
@@ -4335,7 +4335,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
@@ -4343,7 +4343,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>437</v>
+        <v>365</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
@@ -4351,7 +4351,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.3">
@@ -4359,7 +4359,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.3">
@@ -4367,7 +4367,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>440</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.3">
@@ -4375,7 +4375,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>441</v>
+        <v>369</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.3">
@@ -4383,7 +4383,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>442</v>
+        <v>370</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.3">
@@ -4391,7 +4391,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>443</v>
+        <v>371</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.3">
@@ -4399,7 +4399,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>444</v>
+        <v>372</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.3">
@@ -4407,7 +4407,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>445</v>
+        <v>373</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.3">
@@ -4415,7 +4415,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>446</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.3">
@@ -4423,7 +4423,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>447</v>
+        <v>375</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
@@ -4431,7 +4431,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>448</v>
+        <v>376</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
@@ -4439,7 +4439,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.3">
@@ -4447,7 +4447,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>450</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
@@ -4455,7 +4455,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.3">
@@ -4463,7 +4463,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>452</v>
+        <v>380</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -4471,12 +4471,12 @@
         <v>192</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>193</v>
+        <v>582</v>
       </c>
       <c r="B194">
         <v>2</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>194</v>
+        <v>583</v>
       </c>
       <c r="B195">
         <v>4</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>195</v>
+        <v>584</v>
       </c>
       <c r="B196">
         <v>6</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>196</v>
+        <v>585</v>
       </c>
       <c r="B197" s="2">
         <v>8</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>586</v>
       </c>
       <c r="B198" s="2">
         <v>10</v>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>587</v>
       </c>
       <c r="B199" s="2">
         <v>12</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>199</v>
+        <v>588</v>
       </c>
       <c r="B200" s="2">
         <v>14</v>
@@ -4538,7 +4538,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>589</v>
       </c>
       <c r="B201" s="2">
         <v>16</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>590</v>
       </c>
       <c r="B202" s="2">
         <v>18</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>202</v>
+        <v>591</v>
       </c>
       <c r="B203">
         <v>3</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>203</v>
+        <v>592</v>
       </c>
       <c r="B204">
         <v>6</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>204</v>
+        <v>593</v>
       </c>
       <c r="B205">
         <v>9</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>205</v>
+        <v>594</v>
       </c>
       <c r="B206" s="2">
         <v>12</v>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>206</v>
+        <v>595</v>
       </c>
       <c r="B207" s="2">
         <v>15</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>207</v>
+        <v>596</v>
       </c>
       <c r="B208" s="2">
         <v>18</v>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>208</v>
+        <v>597</v>
       </c>
       <c r="B209" s="2">
         <v>21</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>209</v>
+        <v>598</v>
       </c>
       <c r="B210" s="2">
         <v>24</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>210</v>
+        <v>599</v>
       </c>
       <c r="B211" s="2">
         <v>27</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>211</v>
+        <v>600</v>
       </c>
       <c r="B212">
         <v>4</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="B213">
         <v>8</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>213</v>
+        <v>602</v>
       </c>
       <c r="B214">
         <v>12</v>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>214</v>
+        <v>603</v>
       </c>
       <c r="B215">
         <v>16</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>215</v>
+        <v>604</v>
       </c>
       <c r="B216" s="2">
         <v>20</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>216</v>
+        <v>605</v>
       </c>
       <c r="B217" s="2">
         <v>24</v>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>217</v>
+        <v>606</v>
       </c>
       <c r="B218" s="2">
         <v>28</v>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>218</v>
+        <v>607</v>
       </c>
       <c r="B219" s="2">
         <v>32</v>
@@ -4705,7 +4705,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>219</v>
+        <v>608</v>
       </c>
       <c r="B220" s="2">
         <v>36</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>220</v>
+        <v>609</v>
       </c>
       <c r="B221">
         <v>5</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>221</v>
+        <v>610</v>
       </c>
       <c r="B222">
         <v>10</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>222</v>
+        <v>611</v>
       </c>
       <c r="B223">
         <v>15</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>223</v>
+        <v>612</v>
       </c>
       <c r="B224">
         <v>20</v>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>224</v>
+        <v>613</v>
       </c>
       <c r="B225">
         <v>25</v>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>225</v>
+        <v>614</v>
       </c>
       <c r="B226" s="2">
         <v>30</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>226</v>
+        <v>615</v>
       </c>
       <c r="B227" s="2">
         <v>35</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>227</v>
+        <v>616</v>
       </c>
       <c r="B228" s="2">
         <v>40</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>228</v>
+        <v>617</v>
       </c>
       <c r="B229" s="2">
         <v>45</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>229</v>
+        <v>618</v>
       </c>
       <c r="B230">
         <v>6</v>
@@ -4804,7 +4804,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>619</v>
       </c>
       <c r="B231">
         <v>12</v>
@@ -4813,7 +4813,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>231</v>
+        <v>620</v>
       </c>
       <c r="B232">
         <v>18</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>621</v>
       </c>
       <c r="B233">
         <v>24</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>233</v>
+        <v>622</v>
       </c>
       <c r="B234">
         <v>30</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>234</v>
+        <v>623</v>
       </c>
       <c r="B235" s="2">
         <v>36</v>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>624</v>
       </c>
       <c r="B236" s="2">
         <v>42</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>236</v>
+        <v>625</v>
       </c>
       <c r="B237" s="2">
         <v>48</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>237</v>
+        <v>626</v>
       </c>
       <c r="B238" s="2">
         <v>54</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>238</v>
+        <v>627</v>
       </c>
       <c r="B239">
         <v>7</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>239</v>
+        <v>628</v>
       </c>
       <c r="B240">
         <v>14</v>
@@ -4894,7 +4894,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>240</v>
+        <v>629</v>
       </c>
       <c r="B241">
         <v>21</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>241</v>
+        <v>630</v>
       </c>
       <c r="B242">
         <v>28</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>242</v>
+        <v>631</v>
       </c>
       <c r="B243">
         <v>35</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>243</v>
+        <v>632</v>
       </c>
       <c r="B244" s="2">
         <v>42</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>244</v>
+        <v>633</v>
       </c>
       <c r="B245" s="2">
         <v>49</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>245</v>
+        <v>634</v>
       </c>
       <c r="B246" s="2">
         <v>56</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>246</v>
+        <v>635</v>
       </c>
       <c r="B247" s="2">
         <v>63</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>247</v>
+        <v>636</v>
       </c>
       <c r="B248">
         <v>8</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>248</v>
+        <v>637</v>
       </c>
       <c r="B249">
         <v>16</v>
@@ -4975,7 +4975,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>249</v>
+        <v>638</v>
       </c>
       <c r="B250">
         <v>24</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>250</v>
+        <v>639</v>
       </c>
       <c r="B251" s="2">
         <v>32</v>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>251</v>
+        <v>640</v>
       </c>
       <c r="B252" s="2">
         <v>40</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>252</v>
+        <v>641</v>
       </c>
       <c r="B253" s="2">
         <v>48</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>253</v>
+        <v>642</v>
       </c>
       <c r="B254" s="2">
         <v>56</v>
@@ -5020,7 +5020,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>643</v>
       </c>
       <c r="B255" s="2">
         <v>64</v>
@@ -5029,7 +5029,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>255</v>
+        <v>644</v>
       </c>
       <c r="B256" s="2">
         <v>72</v>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>256</v>
+        <v>645</v>
       </c>
       <c r="B257">
         <v>9</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>257</v>
+        <v>646</v>
       </c>
       <c r="B258">
         <v>18</v>
@@ -5056,7 +5056,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>258</v>
+        <v>647</v>
       </c>
       <c r="B259">
         <v>27</v>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>259</v>
+        <v>648</v>
       </c>
       <c r="B260" s="2">
         <v>36</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>260</v>
+        <v>649</v>
       </c>
       <c r="B261" s="2">
         <v>45</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>261</v>
+        <v>650</v>
       </c>
       <c r="B262" s="2">
         <v>54</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>262</v>
+        <v>651</v>
       </c>
       <c r="B263" s="2">
         <v>63</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>263</v>
+        <v>652</v>
       </c>
       <c r="B264" s="2">
         <v>72</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>264</v>
+        <v>653</v>
       </c>
       <c r="B265" s="2">
         <v>81</v>
@@ -5131,982 +5131,982 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>458</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>459</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>461</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>465</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>466</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>467</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>468</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>469</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>470</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>471</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>477</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>478</v>
+        <v>406</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>479</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>480</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>481</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>483</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>485</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>486</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>487</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>492</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>493</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>494</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>495</v>
+        <v>423</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>496</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>497</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>498</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>499</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>500</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>501</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>502</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>503</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>504</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>505</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>506</v>
+        <v>434</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>507</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>508</v>
+        <v>436</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>509</v>
+        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>510</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>511</v>
+        <v>439</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>512</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>513</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>514</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>515</v>
+        <v>443</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>516</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>518</v>
+        <v>446</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>519</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>520</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>521</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>522</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>523</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>524</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>525</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>526</v>
+        <v>454</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>527</v>
+        <v>455</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>528</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>529</v>
+        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>530</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>531</v>
+        <v>459</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>532</v>
+        <v>460</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>533</v>
+        <v>461</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>534</v>
+        <v>462</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>535</v>
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>536</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>537</v>
+        <v>465</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>539</v>
+        <v>467</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>540</v>
+        <v>468</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>541</v>
+        <v>469</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>542</v>
+        <v>470</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>543</v>
+        <v>471</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>544</v>
+        <v>472</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>545</v>
+        <v>473</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>546</v>
+        <v>474</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>547</v>
+        <v>475</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>548</v>
+        <v>476</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>549</v>
+        <v>477</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>550</v>
+        <v>478</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>551</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>552</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>553</v>
+        <v>481</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>554</v>
+        <v>482</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>555</v>
+        <v>483</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>556</v>
+        <v>484</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>557</v>
+        <v>485</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>558</v>
+        <v>486</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>559</v>
+        <v>487</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>560</v>
+        <v>488</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>561</v>
+        <v>489</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>562</v>
+        <v>490</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>563</v>
+        <v>491</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>564</v>
+        <v>492</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>565</v>
+        <v>493</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>566</v>
+        <v>494</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>567</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>568</v>
+        <v>496</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>569</v>
+        <v>497</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>570</v>
+        <v>498</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>571</v>
+        <v>499</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>572</v>
+        <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>573</v>
+        <v>501</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>574</v>
+        <v>502</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>575</v>
+        <v>503</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>576</v>
+        <v>504</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>577</v>
+        <v>505</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>578</v>
+        <v>506</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>579</v>
+        <v>507</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>580</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>581</v>
+        <v>509</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>582</v>
+        <v>510</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>583</v>
+        <v>511</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>584</v>
+        <v>512</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>585</v>
+        <v>513</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>586</v>
+        <v>514</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>587</v>
+        <v>515</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>588</v>
+        <v>516</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>589</v>
+        <v>517</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>590</v>
+        <v>518</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>591</v>
+        <v>519</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>592</v>
+        <v>520</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>593</v>
+        <v>521</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>596</v>
+        <v>524</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>597</v>
+        <v>525</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>598</v>
+        <v>526</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>599</v>
+        <v>527</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>600</v>
+        <v>528</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>601</v>
+        <v>529</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>602</v>
+        <v>530</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>603</v>
+        <v>531</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>604</v>
+        <v>532</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>605</v>
+        <v>533</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>606</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>607</v>
+        <v>535</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>608</v>
+        <v>536</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>609</v>
+        <v>537</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>610</v>
+        <v>538</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>611</v>
+        <v>539</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>612</v>
+        <v>540</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>613</v>
+        <v>541</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>614</v>
+        <v>542</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>615</v>
+        <v>543</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>616</v>
+        <v>544</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>617</v>
+        <v>545</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>618</v>
+        <v>546</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>619</v>
+        <v>547</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>620</v>
+        <v>548</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>621</v>
+        <v>549</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>622</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>623</v>
+        <v>551</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>624</v>
+        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>625</v>
+        <v>553</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>626</v>
+        <v>554</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>627</v>
+        <v>555</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>628</v>
+        <v>556</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>629</v>
+        <v>557</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>630</v>
+        <v>558</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>631</v>
+        <v>559</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>632</v>
+        <v>560</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>633</v>
+        <v>561</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>634</v>
+        <v>562</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>635</v>
+        <v>563</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>636</v>
+        <v>564</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>637</v>
+        <v>565</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>638</v>
+        <v>566</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>639</v>
+        <v>567</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>640</v>
+        <v>568</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>641</v>
+        <v>569</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>642</v>
+        <v>570</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>643</v>
+        <v>571</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>644</v>
+        <v>572</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>645</v>
+        <v>573</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>646</v>
+        <v>574</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>647</v>
+        <v>575</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>648</v>
+        <v>576</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>649</v>
+        <v>577</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>650</v>
+        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>651</v>
+        <v>579</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>652</v>
+        <v>580</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>653</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/flash.xlsx
+++ b/flash.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="2704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="2838">
   <si>
     <t>가나</t>
   </si>
@@ -8133,13 +8133,2123 @@
   </si>
   <si>
     <t>images/1025.png</t>
+  </si>
+  <si>
+    <t>近</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>遠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>가까울 근</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀 원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>短</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짧을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>長</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낮을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>높을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>無</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>有</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>入</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>出</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>强</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굳셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>後</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>少</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>多</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붉을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>황</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>白</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흑</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>兒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>房</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>겨울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>春</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바깥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>外</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>內</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>身</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>심</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>虎</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호랑이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코끼리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>兎</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토끼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>貝</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>패</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舟</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>面</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얼굴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>면</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼻</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>目</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>重</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무거울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>輕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가벼울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>車</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>門</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸를 청</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>靑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>花</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>꽃 화</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>콩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>米</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물고기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>魚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>川</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>江</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>田</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>草</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>풀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>족</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>足</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>兄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8303,6 +10413,23 @@
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="33">
@@ -8732,7 +10859,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8746,6 +10873,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9092,7 +11222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1290"/>
+  <dimension ref="A1:D1357"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="2:3">
@@ -20416,7 +22546,7 @@
       </c>
       <c r="D1280" s="2"/>
     </row>
-    <row r="1281" spans="2:4">
+    <row r="1281" spans="1:4">
       <c r="B1281" s="4" t="s">
         <v>1668</v>
       </c>
@@ -20425,7 +22555,7 @@
       </c>
       <c r="D1281" s="2"/>
     </row>
-    <row r="1282" spans="2:4">
+    <row r="1282" spans="1:4">
       <c r="B1282" s="4" t="s">
         <v>1669</v>
       </c>
@@ -20434,7 +22564,7 @@
       </c>
       <c r="D1282" s="2"/>
     </row>
-    <row r="1283" spans="2:4">
+    <row r="1283" spans="1:4">
       <c r="B1283" s="4" t="s">
         <v>1670</v>
       </c>
@@ -20443,7 +22573,7 @@
       </c>
       <c r="D1283" s="2"/>
     </row>
-    <row r="1284" spans="2:4">
+    <row r="1284" spans="1:4">
       <c r="B1284" s="4" t="s">
         <v>1671</v>
       </c>
@@ -20452,7 +22582,7 @@
       </c>
       <c r="D1284" s="2"/>
     </row>
-    <row r="1285" spans="2:4">
+    <row r="1285" spans="1:4">
       <c r="B1285" s="4" t="s">
         <v>1672</v>
       </c>
@@ -20461,7 +22591,7 @@
       </c>
       <c r="D1285" s="2"/>
     </row>
-    <row r="1286" spans="2:4">
+    <row r="1286" spans="1:4">
       <c r="B1286" s="4" t="s">
         <v>1673</v>
       </c>
@@ -20470,7 +22600,7 @@
       </c>
       <c r="D1286" s="2"/>
     </row>
-    <row r="1287" spans="2:4">
+    <row r="1287" spans="1:4">
       <c r="B1287" s="4" t="s">
         <v>1674</v>
       </c>
@@ -20479,7 +22609,7 @@
       </c>
       <c r="D1287" s="2"/>
     </row>
-    <row r="1288" spans="2:4">
+    <row r="1288" spans="1:4">
       <c r="B1288" s="4" t="s">
         <v>1675</v>
       </c>
@@ -20488,7 +22618,7 @@
       </c>
       <c r="D1288" s="2"/>
     </row>
-    <row r="1289" spans="2:4">
+    <row r="1289" spans="1:4">
       <c r="B1289" s="4" t="s">
         <v>1676</v>
       </c>
@@ -20497,7 +22627,7 @@
       </c>
       <c r="D1289" s="2"/>
     </row>
-    <row r="1290" spans="2:4">
+    <row r="1290" spans="1:4">
       <c r="B1290" s="4" t="s">
         <v>1677</v>
       </c>
@@ -20505,6 +22635,542 @@
         <v>2703</v>
       </c>
       <c r="D1290" s="2"/>
+    </row>
+    <row r="1291" spans="1:4">
+      <c r="A1291" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B1291" s="5" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4">
+      <c r="A1292" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B1292" s="5" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4">
+      <c r="A1293" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B1293" s="4" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4">
+      <c r="A1294" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B1294" s="4" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4">
+      <c r="A1295" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B1295" s="4" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4">
+      <c r="A1296" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B1296" s="4" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:2">
+      <c r="A1297" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B1297" s="4" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2">
+      <c r="A1298" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1298" s="4" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2">
+      <c r="A1299" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B1299" s="4" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:2">
+      <c r="A1300" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1300" s="4" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2">
+      <c r="A1301" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B1301" s="4" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2">
+      <c r="A1302" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1302" s="4" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:2">
+      <c r="A1303" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B1303" s="4" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:2">
+      <c r="A1304" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B1304" s="4" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:2">
+      <c r="A1305" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B1305" s="4" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:2">
+      <c r="A1306" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1306" s="4" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2">
+      <c r="A1307" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B1307" s="4" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2">
+      <c r="A1308" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B1308" s="4" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:2">
+      <c r="A1309" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B1309" s="4" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:2">
+      <c r="A1310" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B1310" s="4" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:2">
+      <c r="A1311" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B1311" s="4" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:2">
+      <c r="A1312" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B1312" s="4" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:2">
+      <c r="A1313" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B1313" s="4" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:2">
+      <c r="A1314" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B1314" s="4" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:2">
+      <c r="A1315" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B1315" s="4" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2">
+      <c r="A1316" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B1316" s="4" t="s">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2">
+      <c r="A1317" t="s">
+        <v>2756</v>
+      </c>
+      <c r="B1317" s="4" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:2">
+      <c r="A1318" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B1318" s="4" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2">
+      <c r="A1319" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B1319" s="4" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2">
+      <c r="A1320" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1320" s="4" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2">
+      <c r="A1321" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B1321" s="4" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2">
+      <c r="A1322" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B1322" s="4" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:2">
+      <c r="A1323" t="s">
+        <v>2769</v>
+      </c>
+      <c r="B1323" s="4" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:2">
+      <c r="A1324" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B1324" s="4" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2">
+      <c r="A1325" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B1325" s="4" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2">
+      <c r="A1326" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B1326" s="4" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:2">
+      <c r="A1327" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B1327" s="4" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:2">
+      <c r="A1328" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B1328" s="4" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:2">
+      <c r="A1329" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B1329" s="4" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:2">
+      <c r="A1330" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B1330" s="4" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:2">
+      <c r="A1331" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B1331" s="4" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:2">
+      <c r="A1332" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B1332" s="4" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:2">
+      <c r="A1333" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B1333" s="4" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:2">
+      <c r="A1334" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B1334" s="4" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:2">
+      <c r="A1335" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B1335" s="4" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:2">
+      <c r="A1336" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B1336" s="4" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:2">
+      <c r="A1337" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B1337" s="4" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:2">
+      <c r="A1338" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B1338" s="4" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:2">
+      <c r="A1339" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B1339" s="4" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:2">
+      <c r="A1340" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1340" s="4" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:2">
+      <c r="A1341" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B1341" s="4" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:2">
+      <c r="A1342" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B1342" s="4" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:2">
+      <c r="A1343" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B1343" s="5" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:2">
+      <c r="A1344" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1344" s="5" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:2">
+      <c r="A1345" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1345" s="4" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:2">
+      <c r="A1346" t="s">
+        <v>2814</v>
+      </c>
+      <c r="B1346" s="4" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:2">
+      <c r="A1347" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B1347" s="4" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:2">
+      <c r="A1348" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B1348" s="4" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:2">
+      <c r="A1349" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B1349" s="4" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:2">
+      <c r="A1350" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B1350" s="4" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:2">
+      <c r="A1351" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B1351" s="4" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:2">
+      <c r="A1352" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B1352" s="4" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:2">
+      <c r="A1353" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B1353" s="4" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:2">
+      <c r="A1354" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B1354" s="4" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:2">
+      <c r="A1355" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B1355" s="4" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:2">
+      <c r="A1356" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B1356" s="4" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:2">
+      <c r="A1357" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B1357" s="4" t="s">
+        <v>2836</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
